--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>ING</t>
   </si>
@@ -656,113 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>30890000</v>
+        <v>56828200</v>
       </c>
       <c r="E8" s="3">
-        <v>22908700</v>
+        <v>30978200</v>
       </c>
       <c r="F8" s="3">
-        <v>24627300</v>
+        <v>22974100</v>
       </c>
       <c r="G8" s="3">
-        <v>30872600</v>
+        <v>24697700</v>
       </c>
       <c r="H8" s="3">
-        <v>30540600</v>
+        <v>30960800</v>
       </c>
       <c r="I8" s="3">
-        <v>47809400</v>
+        <v>30627800</v>
       </c>
       <c r="J8" s="3">
+        <v>47946000</v>
+      </c>
+      <c r="K8" s="3">
         <v>47937500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47284500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>54387600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61505000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65900900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>79429400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -802,9 +808,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -844,9 +853,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,9 +962,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,51 +1007,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-771400</v>
+        <v>-733400</v>
       </c>
       <c r="E15" s="3">
-        <v>-904900</v>
+        <v>-773600</v>
       </c>
       <c r="F15" s="3">
-        <v>-899500</v>
+        <v>-907500</v>
       </c>
       <c r="G15" s="3">
-        <v>-855000</v>
+        <v>-902000</v>
       </c>
       <c r="H15" s="3">
-        <v>-786600</v>
+        <v>-857400</v>
       </c>
       <c r="I15" s="3">
-        <v>-751900</v>
+        <v>-788900</v>
       </c>
       <c r="J15" s="3">
+        <v>-754100</v>
+      </c>
+      <c r="K15" s="3">
         <v>-581600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-627800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-650400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-724900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-715900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1015300</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17983900</v>
+        <v>40011600</v>
       </c>
       <c r="E17" s="3">
-        <v>8696300</v>
+        <v>18035300</v>
       </c>
       <c r="F17" s="3">
-        <v>12769400</v>
+        <v>8721100</v>
       </c>
       <c r="G17" s="3">
-        <v>16813200</v>
+        <v>12805800</v>
       </c>
       <c r="H17" s="3">
-        <v>16153500</v>
+        <v>16861200</v>
       </c>
       <c r="I17" s="3">
-        <v>33663200</v>
+        <v>16199600</v>
       </c>
       <c r="J17" s="3">
+        <v>33759400</v>
+      </c>
+      <c r="K17" s="3">
         <v>34627800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35837200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42295000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>50218900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55167900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62059300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>12906100</v>
+        <v>16816600</v>
       </c>
       <c r="E18" s="3">
-        <v>14212400</v>
+        <v>12942900</v>
       </c>
       <c r="F18" s="3">
-        <v>11858000</v>
+        <v>14253000</v>
       </c>
       <c r="G18" s="3">
-        <v>14059400</v>
+        <v>11891800</v>
       </c>
       <c r="H18" s="3">
-        <v>14387100</v>
+        <v>14099600</v>
       </c>
       <c r="I18" s="3">
-        <v>14146200</v>
+        <v>14428200</v>
       </c>
       <c r="J18" s="3">
+        <v>14186600</v>
+      </c>
+      <c r="K18" s="3">
         <v>13309700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11447300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12092700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11286100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10733000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17370000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,92 +1180,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6936400</v>
+        <v>-5400200</v>
       </c>
       <c r="E20" s="3">
-        <v>-6853900</v>
+        <v>-6956200</v>
       </c>
       <c r="F20" s="3">
-        <v>-7725200</v>
+        <v>-6873500</v>
       </c>
       <c r="G20" s="3">
-        <v>-6644500</v>
+        <v>-7747300</v>
       </c>
       <c r="H20" s="3">
-        <v>-6967900</v>
+        <v>-6663500</v>
       </c>
       <c r="I20" s="3">
-        <v>-6260500</v>
+        <v>-6987800</v>
       </c>
       <c r="J20" s="3">
+        <v>-6278300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-6904900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5146900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7907100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4141200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7016200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11411800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6740800</v>
+        <v>12154100</v>
       </c>
       <c r="E21" s="3">
-        <v>8263000</v>
+        <v>6765000</v>
       </c>
       <c r="F21" s="3">
-        <v>5031900</v>
+        <v>8292400</v>
       </c>
       <c r="G21" s="3">
-        <v>8270600</v>
+        <v>5052000</v>
       </c>
       <c r="H21" s="3">
-        <v>7983200</v>
+        <v>8299700</v>
       </c>
       <c r="I21" s="3">
-        <v>8449800</v>
+        <v>8009600</v>
       </c>
       <c r="J21" s="3">
+        <v>8477500</v>
+      </c>
+      <c r="K21" s="3">
         <v>6986100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6935100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4968700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8056200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>7736600</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1273,93 +1312,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>5969700</v>
+        <v>11416300</v>
       </c>
       <c r="E23" s="3">
-        <v>7358500</v>
+        <v>5986700</v>
       </c>
       <c r="F23" s="3">
-        <v>4132800</v>
+        <v>7379500</v>
       </c>
       <c r="G23" s="3">
-        <v>7414900</v>
+        <v>4144600</v>
       </c>
       <c r="H23" s="3">
-        <v>7419200</v>
+        <v>7436100</v>
       </c>
       <c r="I23" s="3">
-        <v>7885800</v>
+        <v>7440400</v>
       </c>
       <c r="J23" s="3">
+        <v>7908300</v>
+      </c>
+      <c r="K23" s="3">
         <v>6404800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6300400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4185600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7144900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3716700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5958300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1871600</v>
+        <v>3231700</v>
       </c>
       <c r="E24" s="3">
-        <v>2036500</v>
+        <v>1877000</v>
       </c>
       <c r="F24" s="3">
-        <v>1351900</v>
+        <v>2042400</v>
       </c>
       <c r="G24" s="3">
-        <v>2121200</v>
+        <v>1355800</v>
       </c>
       <c r="H24" s="3">
-        <v>2199300</v>
+        <v>2127200</v>
       </c>
       <c r="I24" s="3">
-        <v>2474900</v>
+        <v>2205600</v>
       </c>
       <c r="J24" s="3">
+        <v>2482000</v>
+      </c>
+      <c r="K24" s="3">
         <v>1755500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1671000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1096400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1791900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>939900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1232500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4098000</v>
+        <v>8184700</v>
       </c>
       <c r="E26" s="3">
-        <v>5321900</v>
+        <v>4109800</v>
       </c>
       <c r="F26" s="3">
-        <v>2780900</v>
+        <v>5337100</v>
       </c>
       <c r="G26" s="3">
-        <v>5293700</v>
+        <v>2788800</v>
       </c>
       <c r="H26" s="3">
-        <v>5219900</v>
+        <v>5308800</v>
       </c>
       <c r="I26" s="3">
-        <v>5410900</v>
+        <v>5234800</v>
       </c>
       <c r="J26" s="3">
+        <v>5426400</v>
+      </c>
+      <c r="K26" s="3">
         <v>4649200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4629300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3089200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5353000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2776800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4725800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3985200</v>
+        <v>7929000</v>
       </c>
       <c r="E27" s="3">
-        <v>5182000</v>
+        <v>3996600</v>
       </c>
       <c r="F27" s="3">
-        <v>2696200</v>
+        <v>5196800</v>
       </c>
       <c r="G27" s="3">
-        <v>5187400</v>
+        <v>2703900</v>
       </c>
       <c r="H27" s="3">
-        <v>5102800</v>
+        <v>5202200</v>
       </c>
       <c r="I27" s="3">
-        <v>5321900</v>
+        <v>5117300</v>
       </c>
       <c r="J27" s="3">
+        <v>5337100</v>
+      </c>
+      <c r="K27" s="3">
         <v>4567900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4558900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2153200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4628100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1860000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2750200</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1543,33 +1603,36 @@
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>478500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-465500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1587500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>592100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>1405400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1753700</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6936400</v>
+        <v>5400200</v>
       </c>
       <c r="E32" s="3">
-        <v>6853900</v>
+        <v>6956200</v>
       </c>
       <c r="F32" s="3">
-        <v>7725200</v>
+        <v>6873500</v>
       </c>
       <c r="G32" s="3">
-        <v>6644500</v>
+        <v>7747300</v>
       </c>
       <c r="H32" s="3">
-        <v>6967900</v>
+        <v>6663500</v>
       </c>
       <c r="I32" s="3">
-        <v>6260500</v>
+        <v>6987800</v>
       </c>
       <c r="J32" s="3">
+        <v>6278300</v>
+      </c>
+      <c r="K32" s="3">
         <v>6904900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5146900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7907100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4141200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7016200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11411800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3985200</v>
+        <v>7929000</v>
       </c>
       <c r="E33" s="3">
-        <v>5182000</v>
+        <v>3996600</v>
       </c>
       <c r="F33" s="3">
-        <v>2696200</v>
+        <v>5196800</v>
       </c>
       <c r="G33" s="3">
-        <v>5187400</v>
+        <v>2703900</v>
       </c>
       <c r="H33" s="3">
-        <v>5102800</v>
+        <v>5202200</v>
       </c>
       <c r="I33" s="3">
-        <v>5321900</v>
+        <v>5117300</v>
       </c>
       <c r="J33" s="3">
+        <v>5337100</v>
+      </c>
+      <c r="K33" s="3">
         <v>5046300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4093400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>565700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5220200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3265500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4503900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3985200</v>
+        <v>7929000</v>
       </c>
       <c r="E35" s="3">
-        <v>5182000</v>
+        <v>3996600</v>
       </c>
       <c r="F35" s="3">
-        <v>2696200</v>
+        <v>5196800</v>
       </c>
       <c r="G35" s="3">
-        <v>5187400</v>
+        <v>2703900</v>
       </c>
       <c r="H35" s="3">
-        <v>5102800</v>
+        <v>5202200</v>
       </c>
       <c r="I35" s="3">
-        <v>5321900</v>
+        <v>5117300</v>
       </c>
       <c r="J35" s="3">
+        <v>5337100</v>
+      </c>
+      <c r="K35" s="3">
         <v>5046300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4093400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>565700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5220200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3265500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4503900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,92 +1988,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>133149000</v>
+        <v>116343000</v>
       </c>
       <c r="E41" s="3">
-        <v>141172000</v>
+        <v>133530000</v>
       </c>
       <c r="F41" s="3">
-        <v>148049000</v>
+        <v>141575000</v>
       </c>
       <c r="G41" s="3">
-        <v>95846700</v>
+        <v>148472000</v>
       </c>
       <c r="H41" s="3">
-        <v>87243800</v>
+        <v>96120600</v>
       </c>
       <c r="I41" s="3">
-        <v>55118000</v>
+        <v>87493000</v>
       </c>
       <c r="J41" s="3">
+        <v>55275500</v>
+      </c>
+      <c r="K41" s="3">
         <v>50997200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>105032000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>111447000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>134721000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>143923000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>126432000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>124134000</v>
+        <v>134887000</v>
       </c>
       <c r="E42" s="3">
-        <v>111532000</v>
+        <v>124488000</v>
       </c>
       <c r="F42" s="3">
-        <v>113302000</v>
+        <v>111850000</v>
       </c>
       <c r="G42" s="3">
-        <v>104363000</v>
+        <v>113626000</v>
       </c>
       <c r="H42" s="3">
-        <v>130727000</v>
+        <v>104661000</v>
       </c>
       <c r="I42" s="3">
-        <v>133695000</v>
+        <v>131101000</v>
       </c>
       <c r="J42" s="3">
+        <v>134077000</v>
+      </c>
+      <c r="K42" s="3">
         <v>132471000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>140919000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>162702000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>395158000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>256626000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>308386000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2028,9 +2120,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2070,9 +2165,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2112,9 +2210,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2154,135 +2255,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1627500</v>
+        <v>1641900</v>
       </c>
       <c r="E47" s="3">
-        <v>1721900</v>
+        <v>1632200</v>
       </c>
       <c r="F47" s="3">
-        <v>1600400</v>
+        <v>1726800</v>
       </c>
       <c r="G47" s="3">
-        <v>1942100</v>
+        <v>1604900</v>
       </c>
       <c r="H47" s="3">
-        <v>1305300</v>
+        <v>1947700</v>
       </c>
       <c r="I47" s="3">
-        <v>1180500</v>
+        <v>1309000</v>
       </c>
       <c r="J47" s="3">
+        <v>1183900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1238000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>982000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1076000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2418700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7928700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9163900</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2673400</v>
+        <v>2625600</v>
       </c>
       <c r="E48" s="3">
-        <v>2757000</v>
+        <v>2681100</v>
       </c>
       <c r="F48" s="3">
-        <v>3104200</v>
+        <v>2764900</v>
       </c>
       <c r="G48" s="3">
-        <v>3491500</v>
+        <v>3113100</v>
       </c>
       <c r="H48" s="3">
-        <v>1858600</v>
+        <v>3501500</v>
       </c>
       <c r="I48" s="3">
-        <v>2024600</v>
+        <v>1863900</v>
       </c>
       <c r="J48" s="3">
+        <v>2030400</v>
+      </c>
+      <c r="K48" s="3">
         <v>2172200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4216900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4832500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7103000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11519100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10695800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1195700</v>
+        <v>1303500</v>
       </c>
       <c r="E49" s="3">
-        <v>1254300</v>
+        <v>1199100</v>
       </c>
       <c r="F49" s="3">
-        <v>1512500</v>
+        <v>1257800</v>
       </c>
       <c r="G49" s="3">
-        <v>2078900</v>
+        <v>1516800</v>
       </c>
       <c r="H49" s="3">
-        <v>1995300</v>
+        <v>2084800</v>
       </c>
       <c r="I49" s="3">
-        <v>1593900</v>
+        <v>2001000</v>
       </c>
       <c r="J49" s="3">
+        <v>1598400</v>
+      </c>
+      <c r="K49" s="3">
         <v>1610100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2620400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5520200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2418700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8692900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8352800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2618100</v>
+        <v>1995600</v>
       </c>
       <c r="E52" s="3">
-        <v>1887900</v>
+        <v>2625600</v>
       </c>
       <c r="F52" s="3">
-        <v>1625300</v>
+        <v>1893300</v>
       </c>
       <c r="G52" s="3">
-        <v>1561300</v>
+        <v>1630000</v>
       </c>
       <c r="H52" s="3">
-        <v>2853500</v>
+        <v>1565800</v>
       </c>
       <c r="I52" s="3">
-        <v>1475600</v>
+        <v>2861700</v>
       </c>
       <c r="J52" s="3">
+        <v>1479800</v>
+      </c>
+      <c r="K52" s="3">
         <v>1001500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3685100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>188860000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>190519000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>84463700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>91383500</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1050080000</v>
+        <v>1061530000</v>
       </c>
       <c r="E54" s="3">
-        <v>1032150000</v>
+        <v>1053080000</v>
       </c>
       <c r="F54" s="3">
-        <v>1016940000</v>
+        <v>1035100000</v>
       </c>
       <c r="G54" s="3">
-        <v>967542000</v>
+        <v>1019850000</v>
       </c>
       <c r="H54" s="3">
-        <v>962428000</v>
+        <v>970307000</v>
       </c>
       <c r="I54" s="3">
-        <v>918144000</v>
+        <v>965177000</v>
       </c>
       <c r="J54" s="3">
+        <v>920768000</v>
+      </c>
+      <c r="K54" s="3">
         <v>916913000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1026140000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1330820000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1287850000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1271540000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1495710000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,134 +2656,144 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2219900</v>
+        <v>2376400</v>
       </c>
       <c r="E57" s="3">
-        <v>2208000</v>
+        <v>2226300</v>
       </c>
       <c r="F57" s="3">
-        <v>2205800</v>
+        <v>2214300</v>
       </c>
       <c r="G57" s="3">
-        <v>2300200</v>
+        <v>2212100</v>
       </c>
       <c r="H57" s="3">
-        <v>2531300</v>
+        <v>2306800</v>
       </c>
       <c r="I57" s="3">
-        <v>6732400</v>
+        <v>2538500</v>
       </c>
       <c r="J57" s="3">
+        <v>6751700</v>
+      </c>
+      <c r="K57" s="3">
         <v>4767500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5263200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6483300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9421300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11604800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13731200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>40638700</v>
+        <v>53710800</v>
       </c>
       <c r="E58" s="3">
-        <v>41409000</v>
+        <v>40754800</v>
       </c>
       <c r="F58" s="3">
-        <v>29554300</v>
+        <v>41527300</v>
       </c>
       <c r="G58" s="3">
-        <v>56212800</v>
+        <v>29638800</v>
       </c>
       <c r="H58" s="3">
-        <v>60010300</v>
+        <v>56373400</v>
       </c>
       <c r="I58" s="3">
-        <v>48159900</v>
+        <v>60181700</v>
       </c>
       <c r="J58" s="3">
+        <v>48297500</v>
+      </c>
+      <c r="K58" s="3">
         <v>43927300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>52276200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61522400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>63118700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>113681000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1435500</v>
+        <v>1910700</v>
       </c>
       <c r="E59" s="3">
-        <v>1401800</v>
+        <v>1439600</v>
       </c>
       <c r="F59" s="3">
-        <v>1374700</v>
+        <v>1405800</v>
       </c>
       <c r="G59" s="3">
-        <v>1651400</v>
+        <v>1378600</v>
       </c>
       <c r="H59" s="3">
-        <v>1842300</v>
+        <v>1656100</v>
       </c>
       <c r="I59" s="3">
-        <v>1880300</v>
+        <v>1847600</v>
       </c>
       <c r="J59" s="3">
+        <v>1885700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1129500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1179000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1167500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1522800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14712100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16799600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2694,93 +2833,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>81834000</v>
+        <v>99964800</v>
       </c>
       <c r="E61" s="3">
-        <v>77636100</v>
+        <v>82067800</v>
       </c>
       <c r="F61" s="3">
-        <v>78087400</v>
+        <v>77857900</v>
       </c>
       <c r="G61" s="3">
-        <v>92023200</v>
+        <v>78310600</v>
       </c>
       <c r="H61" s="3">
-        <v>84810100</v>
+        <v>92286100</v>
       </c>
       <c r="I61" s="3">
-        <v>73418700</v>
+        <v>85052400</v>
       </c>
       <c r="J61" s="3">
+        <v>73628500</v>
+      </c>
+      <c r="K61" s="3">
         <v>86768500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>88288000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>163166000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>114304000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>185502000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>197673000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1602500</v>
+        <v>1412400</v>
       </c>
       <c r="E62" s="3">
-        <v>2058200</v>
+        <v>1607100</v>
       </c>
       <c r="F62" s="3">
-        <v>1853200</v>
+        <v>2064100</v>
       </c>
       <c r="G62" s="3">
-        <v>2115800</v>
+        <v>1858500</v>
       </c>
       <c r="H62" s="3">
-        <v>2330600</v>
+        <v>2121800</v>
       </c>
       <c r="I62" s="3">
-        <v>3285400</v>
+        <v>2337200</v>
       </c>
       <c r="J62" s="3">
+        <v>3294800</v>
+      </c>
+      <c r="K62" s="3">
         <v>3762800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2148800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3208900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>624400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5090300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7349200</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>995930000</v>
+        <v>1005780000</v>
       </c>
       <c r="E66" s="3">
-        <v>973649000</v>
+        <v>998776000</v>
       </c>
       <c r="F66" s="3">
-        <v>957662000</v>
+        <v>976431000</v>
       </c>
       <c r="G66" s="3">
-        <v>909203000</v>
+        <v>960398000</v>
       </c>
       <c r="H66" s="3">
-        <v>907166000</v>
+        <v>911801000</v>
       </c>
       <c r="I66" s="3">
-        <v>863454000</v>
+        <v>909758000</v>
       </c>
       <c r="J66" s="3">
+        <v>865921000</v>
+      </c>
+      <c r="K66" s="3">
         <v>862888000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>977315000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1272850000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1235490000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1218060000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1441920000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>41824600</v>
+        <v>43416300</v>
       </c>
       <c r="E72" s="3">
-        <v>44194200</v>
+        <v>41944100</v>
       </c>
       <c r="F72" s="3">
-        <v>41691100</v>
+        <v>44320500</v>
       </c>
       <c r="G72" s="3">
-        <v>38899400</v>
+        <v>41810200</v>
       </c>
       <c r="H72" s="3">
-        <v>36020900</v>
+        <v>39010600</v>
       </c>
       <c r="I72" s="3">
-        <v>34205700</v>
+        <v>36123800</v>
       </c>
       <c r="J72" s="3">
+        <v>34303400</v>
+      </c>
+      <c r="K72" s="3">
         <v>31619100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27381900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27824400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24640500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43774000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>46677700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>54151300</v>
+        <v>55754200</v>
       </c>
       <c r="E76" s="3">
-        <v>58501000</v>
+        <v>54306000</v>
       </c>
       <c r="F76" s="3">
-        <v>59281100</v>
+        <v>58668200</v>
       </c>
       <c r="G76" s="3">
-        <v>58339400</v>
+        <v>59450500</v>
       </c>
       <c r="H76" s="3">
-        <v>55261200</v>
+        <v>58506000</v>
       </c>
       <c r="I76" s="3">
-        <v>54690500</v>
+        <v>55419100</v>
       </c>
       <c r="J76" s="3">
+        <v>54846800</v>
+      </c>
+      <c r="K76" s="3">
         <v>54025400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48826900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57972500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52363700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53480300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53792200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3985200</v>
+        <v>7929000</v>
       </c>
       <c r="E81" s="3">
-        <v>5182000</v>
+        <v>3996600</v>
       </c>
       <c r="F81" s="3">
-        <v>2696200</v>
+        <v>5196800</v>
       </c>
       <c r="G81" s="3">
-        <v>5187400</v>
+        <v>2703900</v>
       </c>
       <c r="H81" s="3">
-        <v>5102800</v>
+        <v>5202200</v>
       </c>
       <c r="I81" s="3">
-        <v>5321900</v>
+        <v>5117300</v>
       </c>
       <c r="J81" s="3">
+        <v>5337100</v>
+      </c>
+      <c r="K81" s="3">
         <v>5046300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4093400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>565700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5220200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3265500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4503900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>771400</v>
+        <v>733400</v>
       </c>
       <c r="E83" s="3">
-        <v>904900</v>
+        <v>773600</v>
       </c>
       <c r="F83" s="3">
-        <v>899500</v>
+        <v>907500</v>
       </c>
       <c r="G83" s="3">
-        <v>856100</v>
+        <v>902000</v>
       </c>
       <c r="H83" s="3">
-        <v>564200</v>
+        <v>858500</v>
       </c>
       <c r="I83" s="3">
-        <v>564200</v>
+        <v>565800</v>
       </c>
       <c r="J83" s="3">
+        <v>565800</v>
+      </c>
+      <c r="K83" s="3">
         <v>581600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>647200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>781300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>915100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>1777100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12056500</v>
+        <v>-12339100</v>
       </c>
       <c r="E89" s="3">
-        <v>-16213200</v>
+        <v>-12091000</v>
       </c>
       <c r="F89" s="3">
-        <v>109848700</v>
+        <v>-16259500</v>
       </c>
       <c r="G89" s="3">
-        <v>14164700</v>
+        <v>110162500</v>
       </c>
       <c r="H89" s="3">
-        <v>7502800</v>
+        <v>14205100</v>
       </c>
       <c r="I89" s="3">
-        <v>-5699500</v>
+        <v>7524200</v>
       </c>
       <c r="J89" s="3">
+        <v>-5715800</v>
+      </c>
+      <c r="K89" s="3">
         <v>9280000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10797000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13570700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10069600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10167500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16596500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-250600</v>
+        <v>-267700</v>
       </c>
       <c r="E91" s="3">
-        <v>-199600</v>
+        <v>-251400</v>
       </c>
       <c r="F91" s="3">
-        <v>-311400</v>
+        <v>-200200</v>
       </c>
       <c r="G91" s="3">
-        <v>-385200</v>
+        <v>-312300</v>
       </c>
       <c r="H91" s="3">
-        <v>-310300</v>
+        <v>-386300</v>
       </c>
       <c r="I91" s="3">
-        <v>-329800</v>
+        <v>-311200</v>
       </c>
       <c r="J91" s="3">
+        <v>-330800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-450300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-398100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-461800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-562200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-464500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1980200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5758100</v>
+        <v>-9297800</v>
       </c>
       <c r="E94" s="3">
-        <v>6748700</v>
+        <v>-5774500</v>
       </c>
       <c r="F94" s="3">
-        <v>-9208400</v>
+        <v>6768000</v>
       </c>
       <c r="G94" s="3">
-        <v>-2707100</v>
+        <v>-9234700</v>
       </c>
       <c r="H94" s="3">
-        <v>5914300</v>
+        <v>-2714800</v>
       </c>
       <c r="I94" s="3">
-        <v>12753100</v>
+        <v>5931200</v>
       </c>
       <c r="J94" s="3">
+        <v>12789500</v>
+      </c>
+      <c r="K94" s="3">
         <v>6655400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4283300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8376800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11087600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>7634500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,38 +4222,39 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3311400</v>
+        <v>-3225100</v>
       </c>
       <c r="E96" s="3">
-        <v>-2541100</v>
+        <v>-3320900</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-2548300</v>
       </c>
       <c r="G96" s="3">
-        <v>-2875300</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2828600</v>
+        <v>-2883500</v>
       </c>
       <c r="I96" s="3">
-        <v>-2781900</v>
+        <v>-2836700</v>
       </c>
       <c r="J96" s="3">
+        <v>-2789900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2735300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1422000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>5044200</v>
+        <v>20025400</v>
       </c>
       <c r="E100" s="3">
-        <v>5844900</v>
+        <v>5058600</v>
       </c>
       <c r="F100" s="3">
-        <v>-37753700</v>
+        <v>5861600</v>
       </c>
       <c r="G100" s="3">
-        <v>-4507100</v>
+        <v>-37861500</v>
       </c>
       <c r="H100" s="3">
-        <v>17341600</v>
+        <v>-4520000</v>
       </c>
       <c r="I100" s="3">
-        <v>-4283600</v>
+        <v>17391100</v>
       </c>
       <c r="J100" s="3">
+        <v>-4295800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-20676800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11397200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5265000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10410500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-8135700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-546800</v>
+        <v>-977100</v>
       </c>
       <c r="E101" s="3">
-        <v>-613000</v>
+        <v>-548400</v>
       </c>
       <c r="F101" s="3">
-        <v>-461100</v>
+        <v>-614800</v>
       </c>
       <c r="G101" s="3">
-        <v>103100</v>
+        <v>-462400</v>
       </c>
       <c r="H101" s="3">
-        <v>221300</v>
+        <v>103400</v>
       </c>
       <c r="I101" s="3">
-        <v>282100</v>
+        <v>222000</v>
       </c>
       <c r="J101" s="3">
+        <v>282900</v>
+      </c>
+      <c r="K101" s="3">
         <v>168200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-349100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1055000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-234800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-13317300</v>
+        <v>-2588600</v>
       </c>
       <c r="E102" s="3">
-        <v>-4232600</v>
+        <v>-13355300</v>
       </c>
       <c r="F102" s="3">
-        <v>62425500</v>
+        <v>-4244700</v>
       </c>
       <c r="G102" s="3">
-        <v>7053600</v>
+        <v>62603800</v>
       </c>
       <c r="H102" s="3">
-        <v>30980000</v>
+        <v>7073700</v>
       </c>
       <c r="I102" s="3">
-        <v>3052100</v>
+        <v>31068500</v>
       </c>
       <c r="J102" s="3">
+        <v>3060800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-4573300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3333900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-75600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8337500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-11122700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15860500</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>56828200</v>
+        <v>56441700</v>
       </c>
       <c r="E8" s="3">
-        <v>30978200</v>
+        <v>30767500</v>
       </c>
       <c r="F8" s="3">
-        <v>22974100</v>
+        <v>22817900</v>
       </c>
       <c r="G8" s="3">
-        <v>24697700</v>
+        <v>24529700</v>
       </c>
       <c r="H8" s="3">
-        <v>30960800</v>
+        <v>30750200</v>
       </c>
       <c r="I8" s="3">
-        <v>30627800</v>
+        <v>30419500</v>
       </c>
       <c r="J8" s="3">
-        <v>47946000</v>
+        <v>47620000</v>
       </c>
       <c r="K8" s="3">
         <v>47937500</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-733400</v>
+        <v>-728400</v>
       </c>
       <c r="E15" s="3">
-        <v>-773600</v>
+        <v>-768400</v>
       </c>
       <c r="F15" s="3">
-        <v>-907500</v>
+        <v>-901300</v>
       </c>
       <c r="G15" s="3">
-        <v>-902000</v>
+        <v>-895900</v>
       </c>
       <c r="H15" s="3">
-        <v>-857400</v>
+        <v>-851600</v>
       </c>
       <c r="I15" s="3">
-        <v>-788900</v>
+        <v>-783500</v>
       </c>
       <c r="J15" s="3">
-        <v>-754100</v>
+        <v>-748900</v>
       </c>
       <c r="K15" s="3">
         <v>-581600</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40011600</v>
+        <v>39739500</v>
       </c>
       <c r="E17" s="3">
-        <v>18035300</v>
+        <v>17912600</v>
       </c>
       <c r="F17" s="3">
-        <v>8721100</v>
+        <v>8661800</v>
       </c>
       <c r="G17" s="3">
-        <v>12805800</v>
+        <v>12718800</v>
       </c>
       <c r="H17" s="3">
-        <v>16861200</v>
+        <v>16746500</v>
       </c>
       <c r="I17" s="3">
-        <v>16199600</v>
+        <v>16089500</v>
       </c>
       <c r="J17" s="3">
-        <v>33759400</v>
+        <v>33529800</v>
       </c>
       <c r="K17" s="3">
         <v>34627800</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>16816600</v>
+        <v>16702200</v>
       </c>
       <c r="E18" s="3">
-        <v>12942900</v>
+        <v>12854900</v>
       </c>
       <c r="F18" s="3">
-        <v>14253000</v>
+        <v>14156100</v>
       </c>
       <c r="G18" s="3">
-        <v>11891800</v>
+        <v>11811000</v>
       </c>
       <c r="H18" s="3">
-        <v>14099600</v>
+        <v>14003700</v>
       </c>
       <c r="I18" s="3">
-        <v>14428200</v>
+        <v>14330100</v>
       </c>
       <c r="J18" s="3">
-        <v>14186600</v>
+        <v>14090200</v>
       </c>
       <c r="K18" s="3">
         <v>13309700</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5400200</v>
+        <v>-5363500</v>
       </c>
       <c r="E20" s="3">
-        <v>-6956200</v>
+        <v>-6908900</v>
       </c>
       <c r="F20" s="3">
-        <v>-6873500</v>
+        <v>-6826800</v>
       </c>
       <c r="G20" s="3">
-        <v>-7747300</v>
+        <v>-7694600</v>
       </c>
       <c r="H20" s="3">
-        <v>-6663500</v>
+        <v>-6618200</v>
       </c>
       <c r="I20" s="3">
-        <v>-6987800</v>
+        <v>-6940300</v>
       </c>
       <c r="J20" s="3">
-        <v>-6278300</v>
+        <v>-6235600</v>
       </c>
       <c r="K20" s="3">
         <v>-6904900</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12154100</v>
+        <v>12062500</v>
       </c>
       <c r="E21" s="3">
-        <v>6765000</v>
+        <v>6709500</v>
       </c>
       <c r="F21" s="3">
-        <v>8292400</v>
+        <v>8224900</v>
       </c>
       <c r="G21" s="3">
-        <v>5052000</v>
+        <v>5006600</v>
       </c>
       <c r="H21" s="3">
-        <v>8299700</v>
+        <v>8232800</v>
       </c>
       <c r="I21" s="3">
-        <v>8009600</v>
+        <v>7948200</v>
       </c>
       <c r="J21" s="3">
-        <v>8477500</v>
+        <v>8413000</v>
       </c>
       <c r="K21" s="3">
         <v>6986100</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11416300</v>
+        <v>11338700</v>
       </c>
       <c r="E23" s="3">
-        <v>5986700</v>
+        <v>5946000</v>
       </c>
       <c r="F23" s="3">
-        <v>7379500</v>
+        <v>7329300</v>
       </c>
       <c r="G23" s="3">
-        <v>4144600</v>
+        <v>4116400</v>
       </c>
       <c r="H23" s="3">
-        <v>7436100</v>
+        <v>7385500</v>
       </c>
       <c r="I23" s="3">
-        <v>7440400</v>
+        <v>7389800</v>
       </c>
       <c r="J23" s="3">
-        <v>7908300</v>
+        <v>7854500</v>
       </c>
       <c r="K23" s="3">
         <v>6404800</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3231700</v>
+        <v>3209700</v>
       </c>
       <c r="E24" s="3">
-        <v>1877000</v>
+        <v>1864200</v>
       </c>
       <c r="F24" s="3">
-        <v>2042400</v>
+        <v>2028500</v>
       </c>
       <c r="G24" s="3">
-        <v>1355800</v>
+        <v>1346600</v>
       </c>
       <c r="H24" s="3">
-        <v>2127200</v>
+        <v>2112800</v>
       </c>
       <c r="I24" s="3">
-        <v>2205600</v>
+        <v>2190600</v>
       </c>
       <c r="J24" s="3">
-        <v>2482000</v>
+        <v>2465100</v>
       </c>
       <c r="K24" s="3">
         <v>1755500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8184700</v>
+        <v>8129000</v>
       </c>
       <c r="E26" s="3">
-        <v>4109800</v>
+        <v>4081800</v>
       </c>
       <c r="F26" s="3">
-        <v>5337100</v>
+        <v>5300800</v>
       </c>
       <c r="G26" s="3">
-        <v>2788800</v>
+        <v>2769800</v>
       </c>
       <c r="H26" s="3">
-        <v>5308800</v>
+        <v>5272700</v>
       </c>
       <c r="I26" s="3">
-        <v>5234800</v>
+        <v>5199200</v>
       </c>
       <c r="J26" s="3">
-        <v>5426400</v>
+        <v>5389500</v>
       </c>
       <c r="K26" s="3">
         <v>4649200</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7929000</v>
+        <v>7875100</v>
       </c>
       <c r="E27" s="3">
-        <v>3996600</v>
+        <v>3969400</v>
       </c>
       <c r="F27" s="3">
-        <v>5196800</v>
+        <v>5161400</v>
       </c>
       <c r="G27" s="3">
-        <v>2703900</v>
+        <v>2685500</v>
       </c>
       <c r="H27" s="3">
-        <v>5202200</v>
+        <v>5166800</v>
       </c>
       <c r="I27" s="3">
-        <v>5117300</v>
+        <v>5082500</v>
       </c>
       <c r="J27" s="3">
-        <v>5337100</v>
+        <v>5300800</v>
       </c>
       <c r="K27" s="3">
         <v>4567900</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5400200</v>
+        <v>5363500</v>
       </c>
       <c r="E32" s="3">
-        <v>6956200</v>
+        <v>6908900</v>
       </c>
       <c r="F32" s="3">
-        <v>6873500</v>
+        <v>6826800</v>
       </c>
       <c r="G32" s="3">
-        <v>7747300</v>
+        <v>7694600</v>
       </c>
       <c r="H32" s="3">
-        <v>6663500</v>
+        <v>6618200</v>
       </c>
       <c r="I32" s="3">
-        <v>6987800</v>
+        <v>6940300</v>
       </c>
       <c r="J32" s="3">
-        <v>6278300</v>
+        <v>6235600</v>
       </c>
       <c r="K32" s="3">
         <v>6904900</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7929000</v>
+        <v>7875100</v>
       </c>
       <c r="E33" s="3">
-        <v>3996600</v>
+        <v>3969400</v>
       </c>
       <c r="F33" s="3">
-        <v>5196800</v>
+        <v>5161400</v>
       </c>
       <c r="G33" s="3">
-        <v>2703900</v>
+        <v>2685500</v>
       </c>
       <c r="H33" s="3">
-        <v>5202200</v>
+        <v>5166800</v>
       </c>
       <c r="I33" s="3">
-        <v>5117300</v>
+        <v>5082500</v>
       </c>
       <c r="J33" s="3">
-        <v>5337100</v>
+        <v>5300800</v>
       </c>
       <c r="K33" s="3">
         <v>5046300</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7929000</v>
+        <v>7875100</v>
       </c>
       <c r="E35" s="3">
-        <v>3996600</v>
+        <v>3969400</v>
       </c>
       <c r="F35" s="3">
-        <v>5196800</v>
+        <v>5161400</v>
       </c>
       <c r="G35" s="3">
-        <v>2703900</v>
+        <v>2685500</v>
       </c>
       <c r="H35" s="3">
-        <v>5202200</v>
+        <v>5166800</v>
       </c>
       <c r="I35" s="3">
-        <v>5117300</v>
+        <v>5082500</v>
       </c>
       <c r="J35" s="3">
-        <v>5337100</v>
+        <v>5300800</v>
       </c>
       <c r="K35" s="3">
         <v>5046300</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>116343000</v>
+        <v>115552000</v>
       </c>
       <c r="E41" s="3">
-        <v>133530000</v>
+        <v>132621000</v>
       </c>
       <c r="F41" s="3">
-        <v>141575000</v>
+        <v>140612000</v>
       </c>
       <c r="G41" s="3">
-        <v>148472000</v>
+        <v>147463000</v>
       </c>
       <c r="H41" s="3">
-        <v>96120600</v>
+        <v>95466900</v>
       </c>
       <c r="I41" s="3">
-        <v>87493000</v>
+        <v>86898000</v>
       </c>
       <c r="J41" s="3">
-        <v>55275500</v>
+        <v>54899600</v>
       </c>
       <c r="K41" s="3">
         <v>50997200</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>134887000</v>
+        <v>133970000</v>
       </c>
       <c r="E42" s="3">
-        <v>124488000</v>
+        <v>123642000</v>
       </c>
       <c r="F42" s="3">
-        <v>111850000</v>
+        <v>111090000</v>
       </c>
       <c r="G42" s="3">
-        <v>113626000</v>
+        <v>112853000</v>
       </c>
       <c r="H42" s="3">
-        <v>104661000</v>
+        <v>103949000</v>
       </c>
       <c r="I42" s="3">
-        <v>131101000</v>
+        <v>130209000</v>
       </c>
       <c r="J42" s="3">
-        <v>134077000</v>
+        <v>133165000</v>
       </c>
       <c r="K42" s="3">
         <v>132471000</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1641900</v>
+        <v>1630800</v>
       </c>
       <c r="E47" s="3">
-        <v>1632200</v>
+        <v>1621000</v>
       </c>
       <c r="F47" s="3">
-        <v>1726800</v>
+        <v>1715100</v>
       </c>
       <c r="G47" s="3">
-        <v>1604900</v>
+        <v>1594000</v>
       </c>
       <c r="H47" s="3">
-        <v>1947700</v>
+        <v>1934500</v>
       </c>
       <c r="I47" s="3">
-        <v>1309000</v>
+        <v>1300100</v>
       </c>
       <c r="J47" s="3">
-        <v>1183900</v>
+        <v>1175800</v>
       </c>
       <c r="K47" s="3">
         <v>1238000</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2625600</v>
+        <v>2607700</v>
       </c>
       <c r="E48" s="3">
-        <v>2681100</v>
+        <v>2662800</v>
       </c>
       <c r="F48" s="3">
-        <v>2764900</v>
+        <v>2746100</v>
       </c>
       <c r="G48" s="3">
-        <v>3113100</v>
+        <v>3091900</v>
       </c>
       <c r="H48" s="3">
-        <v>3501500</v>
+        <v>3477700</v>
       </c>
       <c r="I48" s="3">
-        <v>1863900</v>
+        <v>1851200</v>
       </c>
       <c r="J48" s="3">
-        <v>2030400</v>
+        <v>2016600</v>
       </c>
       <c r="K48" s="3">
         <v>2172200</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1303500</v>
+        <v>1294700</v>
       </c>
       <c r="E49" s="3">
-        <v>1199100</v>
+        <v>1190900</v>
       </c>
       <c r="F49" s="3">
-        <v>1257800</v>
+        <v>1249300</v>
       </c>
       <c r="G49" s="3">
-        <v>1516800</v>
+        <v>1506500</v>
       </c>
       <c r="H49" s="3">
-        <v>2084800</v>
+        <v>2070600</v>
       </c>
       <c r="I49" s="3">
-        <v>2001000</v>
+        <v>1987400</v>
       </c>
       <c r="J49" s="3">
-        <v>1598400</v>
+        <v>1587500</v>
       </c>
       <c r="K49" s="3">
         <v>1610100</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1995600</v>
+        <v>1982000</v>
       </c>
       <c r="E52" s="3">
-        <v>2625600</v>
+        <v>2607700</v>
       </c>
       <c r="F52" s="3">
-        <v>1893300</v>
+        <v>1880400</v>
       </c>
       <c r="G52" s="3">
-        <v>1630000</v>
+        <v>1618900</v>
       </c>
       <c r="H52" s="3">
-        <v>1565800</v>
+        <v>1555100</v>
       </c>
       <c r="I52" s="3">
-        <v>2861700</v>
+        <v>2842200</v>
       </c>
       <c r="J52" s="3">
-        <v>1479800</v>
+        <v>1469800</v>
       </c>
       <c r="K52" s="3">
         <v>1001500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1061530000</v>
+        <v>1054310000</v>
       </c>
       <c r="E54" s="3">
-        <v>1053080000</v>
+        <v>1045920000</v>
       </c>
       <c r="F54" s="3">
-        <v>1035100000</v>
+        <v>1028060000</v>
       </c>
       <c r="G54" s="3">
-        <v>1019850000</v>
+        <v>1012910000</v>
       </c>
       <c r="H54" s="3">
-        <v>970307000</v>
+        <v>963708000</v>
       </c>
       <c r="I54" s="3">
-        <v>965177000</v>
+        <v>958613000</v>
       </c>
       <c r="J54" s="3">
-        <v>920768000</v>
+        <v>914506000</v>
       </c>
       <c r="K54" s="3">
         <v>916913000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2376400</v>
+        <v>2360200</v>
       </c>
       <c r="E57" s="3">
-        <v>2226300</v>
+        <v>2211100</v>
       </c>
       <c r="F57" s="3">
-        <v>2214300</v>
+        <v>2199200</v>
       </c>
       <c r="G57" s="3">
-        <v>2212100</v>
+        <v>2197100</v>
       </c>
       <c r="H57" s="3">
-        <v>2306800</v>
+        <v>2291100</v>
       </c>
       <c r="I57" s="3">
-        <v>2538500</v>
+        <v>2521300</v>
       </c>
       <c r="J57" s="3">
-        <v>6751700</v>
+        <v>6705700</v>
       </c>
       <c r="K57" s="3">
         <v>4767500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53710800</v>
+        <v>53345500</v>
       </c>
       <c r="E58" s="3">
-        <v>40754800</v>
+        <v>40477600</v>
       </c>
       <c r="F58" s="3">
-        <v>41527300</v>
+        <v>41244900</v>
       </c>
       <c r="G58" s="3">
-        <v>29638800</v>
+        <v>29437200</v>
       </c>
       <c r="H58" s="3">
-        <v>56373400</v>
+        <v>55990000</v>
       </c>
       <c r="I58" s="3">
-        <v>60181700</v>
+        <v>59772400</v>
       </c>
       <c r="J58" s="3">
-        <v>48297500</v>
+        <v>47969000</v>
       </c>
       <c r="K58" s="3">
         <v>43927300</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1910700</v>
+        <v>1897700</v>
       </c>
       <c r="E59" s="3">
-        <v>1439600</v>
+        <v>1429800</v>
       </c>
       <c r="F59" s="3">
-        <v>1405800</v>
+        <v>1396300</v>
       </c>
       <c r="G59" s="3">
-        <v>1378600</v>
+        <v>1369200</v>
       </c>
       <c r="H59" s="3">
-        <v>1656100</v>
+        <v>1644800</v>
       </c>
       <c r="I59" s="3">
-        <v>1847600</v>
+        <v>1835000</v>
       </c>
       <c r="J59" s="3">
-        <v>1885700</v>
+        <v>1872900</v>
       </c>
       <c r="K59" s="3">
         <v>1129500</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>99964800</v>
+        <v>99285000</v>
       </c>
       <c r="E61" s="3">
-        <v>82067800</v>
+        <v>81509600</v>
       </c>
       <c r="F61" s="3">
-        <v>77857900</v>
+        <v>77328400</v>
       </c>
       <c r="G61" s="3">
-        <v>78310600</v>
+        <v>77778000</v>
       </c>
       <c r="H61" s="3">
-        <v>92286100</v>
+        <v>91658500</v>
       </c>
       <c r="I61" s="3">
-        <v>85052400</v>
+        <v>84474000</v>
       </c>
       <c r="J61" s="3">
-        <v>73628500</v>
+        <v>73127700</v>
       </c>
       <c r="K61" s="3">
         <v>86768500</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1412400</v>
+        <v>1402700</v>
       </c>
       <c r="E62" s="3">
-        <v>1607100</v>
+        <v>1596200</v>
       </c>
       <c r="F62" s="3">
-        <v>2064100</v>
+        <v>2050100</v>
       </c>
       <c r="G62" s="3">
-        <v>1858500</v>
+        <v>1845800</v>
       </c>
       <c r="H62" s="3">
-        <v>2121800</v>
+        <v>2107400</v>
       </c>
       <c r="I62" s="3">
-        <v>2337200</v>
+        <v>2321300</v>
       </c>
       <c r="J62" s="3">
-        <v>3294800</v>
+        <v>3272400</v>
       </c>
       <c r="K62" s="3">
         <v>3762800</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1005780000</v>
+        <v>998938000</v>
       </c>
       <c r="E66" s="3">
-        <v>998776000</v>
+        <v>991983000</v>
       </c>
       <c r="F66" s="3">
-        <v>976431000</v>
+        <v>969790000</v>
       </c>
       <c r="G66" s="3">
-        <v>960398000</v>
+        <v>953867000</v>
       </c>
       <c r="H66" s="3">
-        <v>911801000</v>
+        <v>905600000</v>
       </c>
       <c r="I66" s="3">
-        <v>909758000</v>
+        <v>903571000</v>
       </c>
       <c r="J66" s="3">
-        <v>865921000</v>
+        <v>860032000</v>
       </c>
       <c r="K66" s="3">
         <v>862888000</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>43416300</v>
+        <v>43121000</v>
       </c>
       <c r="E72" s="3">
-        <v>41944100</v>
+        <v>41658800</v>
       </c>
       <c r="F72" s="3">
-        <v>44320500</v>
+        <v>44019100</v>
       </c>
       <c r="G72" s="3">
-        <v>41810200</v>
+        <v>41525900</v>
       </c>
       <c r="H72" s="3">
-        <v>39010600</v>
+        <v>38745300</v>
       </c>
       <c r="I72" s="3">
-        <v>36123800</v>
+        <v>35878200</v>
       </c>
       <c r="J72" s="3">
-        <v>34303400</v>
+        <v>34070100</v>
       </c>
       <c r="K72" s="3">
         <v>31619100</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>55754200</v>
+        <v>55375100</v>
       </c>
       <c r="E76" s="3">
-        <v>54306000</v>
+        <v>53936700</v>
       </c>
       <c r="F76" s="3">
-        <v>58668200</v>
+        <v>58269200</v>
       </c>
       <c r="G76" s="3">
-        <v>59450500</v>
+        <v>59046200</v>
       </c>
       <c r="H76" s="3">
-        <v>58506000</v>
+        <v>58108200</v>
       </c>
       <c r="I76" s="3">
-        <v>55419100</v>
+        <v>55042200</v>
       </c>
       <c r="J76" s="3">
-        <v>54846800</v>
+        <v>54473800</v>
       </c>
       <c r="K76" s="3">
         <v>54025400</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7929000</v>
+        <v>7875100</v>
       </c>
       <c r="E81" s="3">
-        <v>3996600</v>
+        <v>3969400</v>
       </c>
       <c r="F81" s="3">
-        <v>5196800</v>
+        <v>5161400</v>
       </c>
       <c r="G81" s="3">
-        <v>2703900</v>
+        <v>2685500</v>
       </c>
       <c r="H81" s="3">
-        <v>5202200</v>
+        <v>5166800</v>
       </c>
       <c r="I81" s="3">
-        <v>5117300</v>
+        <v>5082500</v>
       </c>
       <c r="J81" s="3">
-        <v>5337100</v>
+        <v>5300800</v>
       </c>
       <c r="K81" s="3">
         <v>5046300</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>733400</v>
+        <v>728400</v>
       </c>
       <c r="E83" s="3">
-        <v>773600</v>
+        <v>768400</v>
       </c>
       <c r="F83" s="3">
-        <v>907500</v>
+        <v>901300</v>
       </c>
       <c r="G83" s="3">
-        <v>902000</v>
+        <v>895900</v>
       </c>
       <c r="H83" s="3">
-        <v>858500</v>
+        <v>852700</v>
       </c>
       <c r="I83" s="3">
-        <v>565800</v>
+        <v>562000</v>
       </c>
       <c r="J83" s="3">
-        <v>565800</v>
+        <v>562000</v>
       </c>
       <c r="K83" s="3">
         <v>581600</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12339100</v>
+        <v>-12255100</v>
       </c>
       <c r="E89" s="3">
-        <v>-12091000</v>
+        <v>-12008700</v>
       </c>
       <c r="F89" s="3">
-        <v>-16259500</v>
+        <v>-16148900</v>
       </c>
       <c r="G89" s="3">
-        <v>110162500</v>
+        <v>109413300</v>
       </c>
       <c r="H89" s="3">
-        <v>14205100</v>
+        <v>14108500</v>
       </c>
       <c r="I89" s="3">
-        <v>7524200</v>
+        <v>7473000</v>
       </c>
       <c r="J89" s="3">
-        <v>-5715800</v>
+        <v>-5676900</v>
       </c>
       <c r="K89" s="3">
         <v>9280000</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-267700</v>
+        <v>-265900</v>
       </c>
       <c r="E91" s="3">
-        <v>-251400</v>
+        <v>-249600</v>
       </c>
       <c r="F91" s="3">
-        <v>-200200</v>
+        <v>-198800</v>
       </c>
       <c r="G91" s="3">
-        <v>-312300</v>
+        <v>-310200</v>
       </c>
       <c r="H91" s="3">
-        <v>-386300</v>
+        <v>-383600</v>
       </c>
       <c r="I91" s="3">
-        <v>-311200</v>
+        <v>-309100</v>
       </c>
       <c r="J91" s="3">
-        <v>-330800</v>
+        <v>-328500</v>
       </c>
       <c r="K91" s="3">
         <v>-450300</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9297800</v>
+        <v>-9234600</v>
       </c>
       <c r="E94" s="3">
-        <v>-5774500</v>
+        <v>-5735300</v>
       </c>
       <c r="F94" s="3">
-        <v>6768000</v>
+        <v>6722000</v>
       </c>
       <c r="G94" s="3">
-        <v>-9234700</v>
+        <v>-9171900</v>
       </c>
       <c r="H94" s="3">
-        <v>-2714800</v>
+        <v>-2696300</v>
       </c>
       <c r="I94" s="3">
-        <v>5931200</v>
+        <v>5890900</v>
       </c>
       <c r="J94" s="3">
-        <v>12789500</v>
+        <v>12702500</v>
       </c>
       <c r="K94" s="3">
         <v>6655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3225100</v>
+        <v>-3203200</v>
       </c>
       <c r="E96" s="3">
-        <v>-3320900</v>
+        <v>-3298300</v>
       </c>
       <c r="F96" s="3">
-        <v>-2548300</v>
+        <v>-2531000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2883500</v>
+        <v>-2863900</v>
       </c>
       <c r="I96" s="3">
-        <v>-2836700</v>
+        <v>-2817400</v>
       </c>
       <c r="J96" s="3">
-        <v>-2789900</v>
+        <v>-2770900</v>
       </c>
       <c r="K96" s="3">
         <v>-2735300</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>20025400</v>
+        <v>19889200</v>
       </c>
       <c r="E100" s="3">
-        <v>5058600</v>
+        <v>5024200</v>
       </c>
       <c r="F100" s="3">
-        <v>5861600</v>
+        <v>5821700</v>
       </c>
       <c r="G100" s="3">
-        <v>-37861500</v>
+        <v>-37604000</v>
       </c>
       <c r="H100" s="3">
-        <v>-4520000</v>
+        <v>-4489200</v>
       </c>
       <c r="I100" s="3">
-        <v>17391100</v>
+        <v>17272800</v>
       </c>
       <c r="J100" s="3">
-        <v>-4295800</v>
+        <v>-4266600</v>
       </c>
       <c r="K100" s="3">
         <v>-20676800</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-977100</v>
+        <v>-970500</v>
       </c>
       <c r="E101" s="3">
-        <v>-548400</v>
+        <v>-544700</v>
       </c>
       <c r="F101" s="3">
-        <v>-614800</v>
+        <v>-610600</v>
       </c>
       <c r="G101" s="3">
-        <v>-462400</v>
+        <v>-459300</v>
       </c>
       <c r="H101" s="3">
-        <v>103400</v>
+        <v>102700</v>
       </c>
       <c r="I101" s="3">
-        <v>222000</v>
+        <v>220500</v>
       </c>
       <c r="J101" s="3">
-        <v>282900</v>
+        <v>281000</v>
       </c>
       <c r="K101" s="3">
         <v>168200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2588600</v>
+        <v>-2571000</v>
       </c>
       <c r="E102" s="3">
-        <v>-13355300</v>
+        <v>-13264500</v>
       </c>
       <c r="F102" s="3">
-        <v>-4244700</v>
+        <v>-4215800</v>
       </c>
       <c r="G102" s="3">
-        <v>62603800</v>
+        <v>62178100</v>
       </c>
       <c r="H102" s="3">
-        <v>7073700</v>
+        <v>7025600</v>
       </c>
       <c r="I102" s="3">
-        <v>31068500</v>
+        <v>30857200</v>
       </c>
       <c r="J102" s="3">
-        <v>3060800</v>
+        <v>3040000</v>
       </c>
       <c r="K102" s="3">
         <v>-4573300</v>

--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>56441700</v>
+        <v>57846600</v>
       </c>
       <c r="E8" s="3">
-        <v>30767500</v>
+        <v>31533400</v>
       </c>
       <c r="F8" s="3">
-        <v>22817900</v>
+        <v>23385900</v>
       </c>
       <c r="G8" s="3">
-        <v>24529700</v>
+        <v>25140300</v>
       </c>
       <c r="H8" s="3">
-        <v>30750200</v>
+        <v>31515700</v>
       </c>
       <c r="I8" s="3">
-        <v>30419500</v>
+        <v>31176700</v>
       </c>
       <c r="J8" s="3">
-        <v>47620000</v>
+        <v>48805300</v>
       </c>
       <c r="K8" s="3">
         <v>47937500</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-728400</v>
+        <v>-746500</v>
       </c>
       <c r="E15" s="3">
-        <v>-768400</v>
+        <v>-787500</v>
       </c>
       <c r="F15" s="3">
-        <v>-901300</v>
+        <v>-923700</v>
       </c>
       <c r="G15" s="3">
-        <v>-895900</v>
+        <v>-918200</v>
       </c>
       <c r="H15" s="3">
-        <v>-851600</v>
+        <v>-872800</v>
       </c>
       <c r="I15" s="3">
-        <v>-783500</v>
+        <v>-803000</v>
       </c>
       <c r="J15" s="3">
-        <v>-748900</v>
+        <v>-767600</v>
       </c>
       <c r="K15" s="3">
         <v>-581600</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>39739500</v>
+        <v>40728700</v>
       </c>
       <c r="E17" s="3">
-        <v>17912600</v>
+        <v>18358500</v>
       </c>
       <c r="F17" s="3">
-        <v>8661800</v>
+        <v>8877400</v>
       </c>
       <c r="G17" s="3">
-        <v>12718800</v>
+        <v>13035300</v>
       </c>
       <c r="H17" s="3">
-        <v>16746500</v>
+        <v>17163400</v>
       </c>
       <c r="I17" s="3">
-        <v>16089500</v>
+        <v>16489900</v>
       </c>
       <c r="J17" s="3">
-        <v>33529800</v>
+        <v>34364400</v>
       </c>
       <c r="K17" s="3">
         <v>34627800</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>16702200</v>
+        <v>17118000</v>
       </c>
       <c r="E18" s="3">
-        <v>12854900</v>
+        <v>13174900</v>
       </c>
       <c r="F18" s="3">
-        <v>14156100</v>
+        <v>14508500</v>
       </c>
       <c r="G18" s="3">
-        <v>11811000</v>
+        <v>12105000</v>
       </c>
       <c r="H18" s="3">
-        <v>14003700</v>
+        <v>14352300</v>
       </c>
       <c r="I18" s="3">
-        <v>14330100</v>
+        <v>14686800</v>
       </c>
       <c r="J18" s="3">
-        <v>14090200</v>
+        <v>14440900</v>
       </c>
       <c r="K18" s="3">
         <v>13309700</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5363500</v>
+        <v>-5497000</v>
       </c>
       <c r="E20" s="3">
-        <v>-6908900</v>
+        <v>-7080900</v>
       </c>
       <c r="F20" s="3">
-        <v>-6826800</v>
+        <v>-6996700</v>
       </c>
       <c r="G20" s="3">
-        <v>-7694600</v>
+        <v>-7886100</v>
       </c>
       <c r="H20" s="3">
-        <v>-6618200</v>
+        <v>-6782900</v>
       </c>
       <c r="I20" s="3">
-        <v>-6940300</v>
+        <v>-7113000</v>
       </c>
       <c r="J20" s="3">
-        <v>-6235600</v>
+        <v>-6390900</v>
       </c>
       <c r="K20" s="3">
         <v>-6904900</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12062500</v>
+        <v>12367300</v>
       </c>
       <c r="E21" s="3">
-        <v>6709500</v>
+        <v>6881400</v>
       </c>
       <c r="F21" s="3">
-        <v>8224900</v>
+        <v>8435300</v>
       </c>
       <c r="G21" s="3">
-        <v>5006600</v>
+        <v>5136900</v>
       </c>
       <c r="H21" s="3">
-        <v>8232800</v>
+        <v>8443100</v>
       </c>
       <c r="I21" s="3">
-        <v>7948200</v>
+        <v>8149600</v>
       </c>
       <c r="J21" s="3">
-        <v>8413000</v>
+        <v>8625900</v>
       </c>
       <c r="K21" s="3">
         <v>6986100</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11338700</v>
+        <v>11620900</v>
       </c>
       <c r="E23" s="3">
-        <v>5946000</v>
+        <v>6094000</v>
       </c>
       <c r="F23" s="3">
-        <v>7329300</v>
+        <v>7511700</v>
       </c>
       <c r="G23" s="3">
-        <v>4116400</v>
+        <v>4218800</v>
       </c>
       <c r="H23" s="3">
-        <v>7385500</v>
+        <v>7569300</v>
       </c>
       <c r="I23" s="3">
-        <v>7389800</v>
+        <v>7573800</v>
       </c>
       <c r="J23" s="3">
-        <v>7854500</v>
+        <v>8050000</v>
       </c>
       <c r="K23" s="3">
         <v>6404800</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3209700</v>
+        <v>3289600</v>
       </c>
       <c r="E24" s="3">
-        <v>1864200</v>
+        <v>1910600</v>
       </c>
       <c r="F24" s="3">
-        <v>2028500</v>
+        <v>2079000</v>
       </c>
       <c r="G24" s="3">
-        <v>1346600</v>
+        <v>1380100</v>
       </c>
       <c r="H24" s="3">
-        <v>2112800</v>
+        <v>2165400</v>
       </c>
       <c r="I24" s="3">
-        <v>2190600</v>
+        <v>2245100</v>
       </c>
       <c r="J24" s="3">
-        <v>2465100</v>
+        <v>2526400</v>
       </c>
       <c r="K24" s="3">
         <v>1755500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8129000</v>
+        <v>8331400</v>
       </c>
       <c r="E26" s="3">
-        <v>4081800</v>
+        <v>4183400</v>
       </c>
       <c r="F26" s="3">
-        <v>5300800</v>
+        <v>5432800</v>
       </c>
       <c r="G26" s="3">
-        <v>2769800</v>
+        <v>2838800</v>
       </c>
       <c r="H26" s="3">
-        <v>5272700</v>
+        <v>5404000</v>
       </c>
       <c r="I26" s="3">
-        <v>5199200</v>
+        <v>5328700</v>
       </c>
       <c r="J26" s="3">
-        <v>5389500</v>
+        <v>5523600</v>
       </c>
       <c r="K26" s="3">
         <v>4649200</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7875100</v>
+        <v>8071100</v>
       </c>
       <c r="E27" s="3">
-        <v>3969400</v>
+        <v>4068200</v>
       </c>
       <c r="F27" s="3">
-        <v>5161400</v>
+        <v>5289900</v>
       </c>
       <c r="G27" s="3">
-        <v>2685500</v>
+        <v>2752400</v>
       </c>
       <c r="H27" s="3">
-        <v>5166800</v>
+        <v>5295400</v>
       </c>
       <c r="I27" s="3">
-        <v>5082500</v>
+        <v>5209000</v>
       </c>
       <c r="J27" s="3">
-        <v>5300800</v>
+        <v>5432800</v>
       </c>
       <c r="K27" s="3">
         <v>4567900</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5363500</v>
+        <v>5497000</v>
       </c>
       <c r="E32" s="3">
-        <v>6908900</v>
+        <v>7080900</v>
       </c>
       <c r="F32" s="3">
-        <v>6826800</v>
+        <v>6996700</v>
       </c>
       <c r="G32" s="3">
-        <v>7694600</v>
+        <v>7886100</v>
       </c>
       <c r="H32" s="3">
-        <v>6618200</v>
+        <v>6782900</v>
       </c>
       <c r="I32" s="3">
-        <v>6940300</v>
+        <v>7113000</v>
       </c>
       <c r="J32" s="3">
-        <v>6235600</v>
+        <v>6390900</v>
       </c>
       <c r="K32" s="3">
         <v>6904900</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7875100</v>
+        <v>8071100</v>
       </c>
       <c r="E33" s="3">
-        <v>3969400</v>
+        <v>4068200</v>
       </c>
       <c r="F33" s="3">
-        <v>5161400</v>
+        <v>5289900</v>
       </c>
       <c r="G33" s="3">
-        <v>2685500</v>
+        <v>2752400</v>
       </c>
       <c r="H33" s="3">
-        <v>5166800</v>
+        <v>5295400</v>
       </c>
       <c r="I33" s="3">
-        <v>5082500</v>
+        <v>5209000</v>
       </c>
       <c r="J33" s="3">
-        <v>5300800</v>
+        <v>5432800</v>
       </c>
       <c r="K33" s="3">
         <v>5046300</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7875100</v>
+        <v>8071100</v>
       </c>
       <c r="E35" s="3">
-        <v>3969400</v>
+        <v>4068200</v>
       </c>
       <c r="F35" s="3">
-        <v>5161400</v>
+        <v>5289900</v>
       </c>
       <c r="G35" s="3">
-        <v>2685500</v>
+        <v>2752400</v>
       </c>
       <c r="H35" s="3">
-        <v>5166800</v>
+        <v>5295400</v>
       </c>
       <c r="I35" s="3">
-        <v>5082500</v>
+        <v>5209000</v>
       </c>
       <c r="J35" s="3">
-        <v>5300800</v>
+        <v>5432800</v>
       </c>
       <c r="K35" s="3">
         <v>5046300</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>115552000</v>
+        <v>118428000</v>
       </c>
       <c r="E41" s="3">
-        <v>132621000</v>
+        <v>135923000</v>
       </c>
       <c r="F41" s="3">
-        <v>140612000</v>
+        <v>144112000</v>
       </c>
       <c r="G41" s="3">
-        <v>147463000</v>
+        <v>151133000</v>
       </c>
       <c r="H41" s="3">
-        <v>95466900</v>
+        <v>97843200</v>
       </c>
       <c r="I41" s="3">
-        <v>86898000</v>
+        <v>89061000</v>
       </c>
       <c r="J41" s="3">
-        <v>54899600</v>
+        <v>56266100</v>
       </c>
       <c r="K41" s="3">
         <v>50997200</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>133970000</v>
+        <v>137305000</v>
       </c>
       <c r="E42" s="3">
-        <v>123642000</v>
+        <v>126719000</v>
       </c>
       <c r="F42" s="3">
-        <v>111090000</v>
+        <v>113855000</v>
       </c>
       <c r="G42" s="3">
-        <v>112853000</v>
+        <v>115662000</v>
       </c>
       <c r="H42" s="3">
-        <v>103949000</v>
+        <v>106537000</v>
       </c>
       <c r="I42" s="3">
-        <v>130209000</v>
+        <v>133450000</v>
       </c>
       <c r="J42" s="3">
-        <v>133165000</v>
+        <v>136480000</v>
       </c>
       <c r="K42" s="3">
         <v>132471000</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1630800</v>
+        <v>1671400</v>
       </c>
       <c r="E47" s="3">
-        <v>1621000</v>
+        <v>1661400</v>
       </c>
       <c r="F47" s="3">
-        <v>1715100</v>
+        <v>1757800</v>
       </c>
       <c r="G47" s="3">
-        <v>1594000</v>
+        <v>1633700</v>
       </c>
       <c r="H47" s="3">
-        <v>1934500</v>
+        <v>1982600</v>
       </c>
       <c r="I47" s="3">
-        <v>1300100</v>
+        <v>1332400</v>
       </c>
       <c r="J47" s="3">
-        <v>1175800</v>
+        <v>1205100</v>
       </c>
       <c r="K47" s="3">
         <v>1238000</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2607700</v>
+        <v>2672600</v>
       </c>
       <c r="E48" s="3">
-        <v>2662800</v>
+        <v>2729100</v>
       </c>
       <c r="F48" s="3">
-        <v>2746100</v>
+        <v>2814400</v>
       </c>
       <c r="G48" s="3">
-        <v>3091900</v>
+        <v>3168800</v>
       </c>
       <c r="H48" s="3">
-        <v>3477700</v>
+        <v>3564300</v>
       </c>
       <c r="I48" s="3">
-        <v>1851200</v>
+        <v>1897300</v>
       </c>
       <c r="J48" s="3">
-        <v>2016600</v>
+        <v>2066800</v>
       </c>
       <c r="K48" s="3">
         <v>2172200</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1294700</v>
+        <v>1326900</v>
       </c>
       <c r="E49" s="3">
-        <v>1190900</v>
+        <v>1220600</v>
       </c>
       <c r="F49" s="3">
-        <v>1249300</v>
+        <v>1280400</v>
       </c>
       <c r="G49" s="3">
-        <v>1506500</v>
+        <v>1544000</v>
       </c>
       <c r="H49" s="3">
-        <v>2070600</v>
+        <v>2122200</v>
       </c>
       <c r="I49" s="3">
-        <v>1987400</v>
+        <v>2036900</v>
       </c>
       <c r="J49" s="3">
-        <v>1587500</v>
+        <v>1627100</v>
       </c>
       <c r="K49" s="3">
         <v>1610100</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1982000</v>
+        <v>2031300</v>
       </c>
       <c r="E52" s="3">
-        <v>2607700</v>
+        <v>2672600</v>
       </c>
       <c r="F52" s="3">
-        <v>1880400</v>
+        <v>1927200</v>
       </c>
       <c r="G52" s="3">
-        <v>1618900</v>
+        <v>1659200</v>
       </c>
       <c r="H52" s="3">
-        <v>1555100</v>
+        <v>1593800</v>
       </c>
       <c r="I52" s="3">
-        <v>2842200</v>
+        <v>2913000</v>
       </c>
       <c r="J52" s="3">
-        <v>1469800</v>
+        <v>1506300</v>
       </c>
       <c r="K52" s="3">
         <v>1001500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1054310000</v>
+        <v>1080560000</v>
       </c>
       <c r="E54" s="3">
-        <v>1045920000</v>
+        <v>1071950000</v>
       </c>
       <c r="F54" s="3">
-        <v>1028060000</v>
+        <v>1053650000</v>
       </c>
       <c r="G54" s="3">
-        <v>1012910000</v>
+        <v>1038130000</v>
       </c>
       <c r="H54" s="3">
-        <v>963708000</v>
+        <v>987696000</v>
       </c>
       <c r="I54" s="3">
-        <v>958613000</v>
+        <v>982474000</v>
       </c>
       <c r="J54" s="3">
-        <v>914506000</v>
+        <v>937269000</v>
       </c>
       <c r="K54" s="3">
         <v>916913000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2360200</v>
+        <v>2419000</v>
       </c>
       <c r="E57" s="3">
-        <v>2211100</v>
+        <v>2266100</v>
       </c>
       <c r="F57" s="3">
-        <v>2199200</v>
+        <v>2254000</v>
       </c>
       <c r="G57" s="3">
-        <v>2197100</v>
+        <v>2251800</v>
       </c>
       <c r="H57" s="3">
-        <v>2291100</v>
+        <v>2348100</v>
       </c>
       <c r="I57" s="3">
-        <v>2521300</v>
+        <v>2584000</v>
       </c>
       <c r="J57" s="3">
-        <v>6705700</v>
+        <v>6872700</v>
       </c>
       <c r="K57" s="3">
         <v>4767500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>53345500</v>
+        <v>54673400</v>
       </c>
       <c r="E58" s="3">
-        <v>40477600</v>
+        <v>41485200</v>
       </c>
       <c r="F58" s="3">
-        <v>41244900</v>
+        <v>42271600</v>
       </c>
       <c r="G58" s="3">
-        <v>29437200</v>
+        <v>30169900</v>
       </c>
       <c r="H58" s="3">
-        <v>55990000</v>
+        <v>57383600</v>
       </c>
       <c r="I58" s="3">
-        <v>59772400</v>
+        <v>61260200</v>
       </c>
       <c r="J58" s="3">
-        <v>47969000</v>
+        <v>49163000</v>
       </c>
       <c r="K58" s="3">
         <v>43927300</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1897700</v>
+        <v>1944900</v>
       </c>
       <c r="E59" s="3">
-        <v>1429800</v>
+        <v>1465400</v>
       </c>
       <c r="F59" s="3">
-        <v>1396300</v>
+        <v>1431000</v>
       </c>
       <c r="G59" s="3">
-        <v>1369200</v>
+        <v>1403300</v>
       </c>
       <c r="H59" s="3">
-        <v>1644800</v>
+        <v>1685800</v>
       </c>
       <c r="I59" s="3">
-        <v>1835000</v>
+        <v>1880700</v>
       </c>
       <c r="J59" s="3">
-        <v>1872900</v>
+        <v>1919500</v>
       </c>
       <c r="K59" s="3">
         <v>1129500</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>99285000</v>
+        <v>101756000</v>
       </c>
       <c r="E61" s="3">
-        <v>81509600</v>
+        <v>83538500</v>
       </c>
       <c r="F61" s="3">
-        <v>77328400</v>
+        <v>79253200</v>
       </c>
       <c r="G61" s="3">
-        <v>77778000</v>
+        <v>79714000</v>
       </c>
       <c r="H61" s="3">
-        <v>91658500</v>
+        <v>93940000</v>
       </c>
       <c r="I61" s="3">
-        <v>84474000</v>
+        <v>86576700</v>
       </c>
       <c r="J61" s="3">
-        <v>73127700</v>
+        <v>74948000</v>
       </c>
       <c r="K61" s="3">
         <v>86768500</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1402700</v>
+        <v>1437700</v>
       </c>
       <c r="E62" s="3">
-        <v>1596200</v>
+        <v>1635900</v>
       </c>
       <c r="F62" s="3">
-        <v>2050100</v>
+        <v>2101100</v>
       </c>
       <c r="G62" s="3">
-        <v>1845800</v>
+        <v>1891800</v>
       </c>
       <c r="H62" s="3">
-        <v>2107400</v>
+        <v>2159800</v>
       </c>
       <c r="I62" s="3">
-        <v>2321300</v>
+        <v>2379100</v>
       </c>
       <c r="J62" s="3">
-        <v>3272400</v>
+        <v>3353800</v>
       </c>
       <c r="K62" s="3">
         <v>3762800</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>998938000</v>
+        <v>1023800000</v>
       </c>
       <c r="E66" s="3">
-        <v>991983000</v>
+        <v>1016670000</v>
       </c>
       <c r="F66" s="3">
-        <v>969790000</v>
+        <v>993929000</v>
       </c>
       <c r="G66" s="3">
-        <v>953867000</v>
+        <v>977610000</v>
       </c>
       <c r="H66" s="3">
-        <v>905600000</v>
+        <v>928141000</v>
       </c>
       <c r="I66" s="3">
-        <v>903571000</v>
+        <v>926062000</v>
       </c>
       <c r="J66" s="3">
-        <v>860032000</v>
+        <v>881439000</v>
       </c>
       <c r="K66" s="3">
         <v>862888000</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>43121000</v>
+        <v>44194300</v>
       </c>
       <c r="E72" s="3">
-        <v>41658800</v>
+        <v>42695800</v>
       </c>
       <c r="F72" s="3">
-        <v>44019100</v>
+        <v>45114800</v>
       </c>
       <c r="G72" s="3">
-        <v>41525900</v>
+        <v>42559500</v>
       </c>
       <c r="H72" s="3">
-        <v>38745300</v>
+        <v>39709700</v>
       </c>
       <c r="I72" s="3">
-        <v>35878200</v>
+        <v>36771200</v>
       </c>
       <c r="J72" s="3">
-        <v>34070100</v>
+        <v>34918200</v>
       </c>
       <c r="K72" s="3">
         <v>31619100</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>55375100</v>
+        <v>56753400</v>
       </c>
       <c r="E76" s="3">
-        <v>53936700</v>
+        <v>55279200</v>
       </c>
       <c r="F76" s="3">
-        <v>58269200</v>
+        <v>59719600</v>
       </c>
       <c r="G76" s="3">
-        <v>59046200</v>
+        <v>60515900</v>
       </c>
       <c r="H76" s="3">
-        <v>58108200</v>
+        <v>59554500</v>
       </c>
       <c r="I76" s="3">
-        <v>55042200</v>
+        <v>56412300</v>
       </c>
       <c r="J76" s="3">
-        <v>54473800</v>
+        <v>55829700</v>
       </c>
       <c r="K76" s="3">
         <v>54025400</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7875100</v>
+        <v>8071100</v>
       </c>
       <c r="E81" s="3">
-        <v>3969400</v>
+        <v>4068200</v>
       </c>
       <c r="F81" s="3">
-        <v>5161400</v>
+        <v>5289900</v>
       </c>
       <c r="G81" s="3">
-        <v>2685500</v>
+        <v>2752400</v>
       </c>
       <c r="H81" s="3">
-        <v>5166800</v>
+        <v>5295400</v>
       </c>
       <c r="I81" s="3">
-        <v>5082500</v>
+        <v>5209000</v>
       </c>
       <c r="J81" s="3">
-        <v>5300800</v>
+        <v>5432800</v>
       </c>
       <c r="K81" s="3">
         <v>5046300</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>728400</v>
+        <v>746500</v>
       </c>
       <c r="E83" s="3">
-        <v>768400</v>
+        <v>787500</v>
       </c>
       <c r="F83" s="3">
-        <v>901300</v>
+        <v>923700</v>
       </c>
       <c r="G83" s="3">
-        <v>895900</v>
+        <v>918200</v>
       </c>
       <c r="H83" s="3">
-        <v>852700</v>
+        <v>873900</v>
       </c>
       <c r="I83" s="3">
-        <v>562000</v>
+        <v>576000</v>
       </c>
       <c r="J83" s="3">
-        <v>562000</v>
+        <v>576000</v>
       </c>
       <c r="K83" s="3">
         <v>581600</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12255100</v>
+        <v>-12560200</v>
       </c>
       <c r="E89" s="3">
-        <v>-12008700</v>
+        <v>-12307700</v>
       </c>
       <c r="F89" s="3">
-        <v>-16148900</v>
+        <v>-16550900</v>
       </c>
       <c r="G89" s="3">
-        <v>109413300</v>
+        <v>112136700</v>
       </c>
       <c r="H89" s="3">
-        <v>14108500</v>
+        <v>14459700</v>
       </c>
       <c r="I89" s="3">
-        <v>7473000</v>
+        <v>7659100</v>
       </c>
       <c r="J89" s="3">
-        <v>-5676900</v>
+        <v>-5818200</v>
       </c>
       <c r="K89" s="3">
         <v>9280000</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-265900</v>
+        <v>-272500</v>
       </c>
       <c r="E91" s="3">
-        <v>-249600</v>
+        <v>-255900</v>
       </c>
       <c r="F91" s="3">
-        <v>-198800</v>
+        <v>-203800</v>
       </c>
       <c r="G91" s="3">
-        <v>-310200</v>
+        <v>-317900</v>
       </c>
       <c r="H91" s="3">
-        <v>-383600</v>
+        <v>-393200</v>
       </c>
       <c r="I91" s="3">
-        <v>-309100</v>
+        <v>-316800</v>
       </c>
       <c r="J91" s="3">
-        <v>-328500</v>
+        <v>-336700</v>
       </c>
       <c r="K91" s="3">
         <v>-450300</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9234600</v>
+        <v>-9464400</v>
       </c>
       <c r="E94" s="3">
-        <v>-5735300</v>
+        <v>-5878000</v>
       </c>
       <c r="F94" s="3">
-        <v>6722000</v>
+        <v>6889300</v>
       </c>
       <c r="G94" s="3">
-        <v>-9171900</v>
+        <v>-9400200</v>
       </c>
       <c r="H94" s="3">
-        <v>-2696300</v>
+        <v>-2763500</v>
       </c>
       <c r="I94" s="3">
-        <v>5890900</v>
+        <v>6037500</v>
       </c>
       <c r="J94" s="3">
-        <v>12702500</v>
+        <v>13018700</v>
       </c>
       <c r="K94" s="3">
         <v>6655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3203200</v>
+        <v>-3282900</v>
       </c>
       <c r="E96" s="3">
-        <v>-3298300</v>
+        <v>-3380400</v>
       </c>
       <c r="F96" s="3">
-        <v>-2531000</v>
+        <v>-2594000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2863900</v>
+        <v>-2935100</v>
       </c>
       <c r="I96" s="3">
-        <v>-2817400</v>
+        <v>-2887500</v>
       </c>
       <c r="J96" s="3">
-        <v>-2770900</v>
+        <v>-2839900</v>
       </c>
       <c r="K96" s="3">
         <v>-2735300</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>19889200</v>
+        <v>20384300</v>
       </c>
       <c r="E100" s="3">
-        <v>5024200</v>
+        <v>5149200</v>
       </c>
       <c r="F100" s="3">
-        <v>5821700</v>
+        <v>5966600</v>
       </c>
       <c r="G100" s="3">
-        <v>-37604000</v>
+        <v>-38540000</v>
       </c>
       <c r="H100" s="3">
-        <v>-4489200</v>
+        <v>-4601000</v>
       </c>
       <c r="I100" s="3">
-        <v>17272800</v>
+        <v>17702800</v>
       </c>
       <c r="J100" s="3">
-        <v>-4266600</v>
+        <v>-4372800</v>
       </c>
       <c r="K100" s="3">
         <v>-20676800</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-970500</v>
+        <v>-994600</v>
       </c>
       <c r="E101" s="3">
-        <v>-544700</v>
+        <v>-558200</v>
       </c>
       <c r="F101" s="3">
-        <v>-610600</v>
+        <v>-625800</v>
       </c>
       <c r="G101" s="3">
-        <v>-459300</v>
+        <v>-470700</v>
       </c>
       <c r="H101" s="3">
-        <v>102700</v>
+        <v>105200</v>
       </c>
       <c r="I101" s="3">
-        <v>220500</v>
+        <v>226000</v>
       </c>
       <c r="J101" s="3">
-        <v>281000</v>
+        <v>288000</v>
       </c>
       <c r="K101" s="3">
         <v>168200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2571000</v>
+        <v>-2635000</v>
       </c>
       <c r="E102" s="3">
-        <v>-13264500</v>
+        <v>-13594700</v>
       </c>
       <c r="F102" s="3">
-        <v>-4215800</v>
+        <v>-4320700</v>
       </c>
       <c r="G102" s="3">
-        <v>62178100</v>
+        <v>63725800</v>
       </c>
       <c r="H102" s="3">
-        <v>7025600</v>
+        <v>7200500</v>
       </c>
       <c r="I102" s="3">
-        <v>30857200</v>
+        <v>31625300</v>
       </c>
       <c r="J102" s="3">
-        <v>3040000</v>
+        <v>3115700</v>
       </c>
       <c r="K102" s="3">
         <v>-4573300</v>

--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>ING</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>57846600</v>
+        <v>19483800</v>
       </c>
       <c r="E8" s="3">
-        <v>31533400</v>
+        <v>31444900</v>
       </c>
       <c r="F8" s="3">
-        <v>23385900</v>
+        <v>22183600</v>
       </c>
       <c r="G8" s="3">
-        <v>25140300</v>
+        <v>17867900</v>
       </c>
       <c r="H8" s="3">
-        <v>31515700</v>
+        <v>19198700</v>
       </c>
       <c r="I8" s="3">
-        <v>31176700</v>
+        <v>20060700</v>
       </c>
       <c r="J8" s="3">
-        <v>48805300</v>
+        <v>21365300</v>
       </c>
       <c r="K8" s="3">
         <v>47937500</v>
@@ -817,26 +817,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>19483800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>31444900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>22183600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>17867900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>19198700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>20060700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>21365300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>320300</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1247100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>299100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>935800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-15700</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>913700</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-129700</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-746500</v>
+        <v>237600</v>
       </c>
       <c r="E15" s="3">
-        <v>-787500</v>
+        <v>249000</v>
       </c>
       <c r="F15" s="3">
-        <v>-923700</v>
+        <v>948500</v>
       </c>
       <c r="G15" s="3">
-        <v>-918200</v>
+        <v>1014100</v>
       </c>
       <c r="H15" s="3">
-        <v>-872800</v>
+        <v>885400</v>
       </c>
       <c r="I15" s="3">
-        <v>-803000</v>
+        <v>595400</v>
       </c>
       <c r="J15" s="3">
-        <v>-767600</v>
+        <v>624400</v>
       </c>
       <c r="K15" s="3">
         <v>-581600</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>40728700</v>
+        <v>12490600</v>
       </c>
       <c r="E17" s="3">
-        <v>18358500</v>
+        <v>11647000</v>
       </c>
       <c r="F17" s="3">
-        <v>8877400</v>
+        <v>12348500</v>
       </c>
       <c r="G17" s="3">
-        <v>13035300</v>
+        <v>12775500</v>
       </c>
       <c r="H17" s="3">
-        <v>17163400</v>
+        <v>11544200</v>
       </c>
       <c r="I17" s="3">
-        <v>16489900</v>
+        <v>11317800</v>
       </c>
       <c r="J17" s="3">
-        <v>34364400</v>
+        <v>11786700</v>
       </c>
       <c r="K17" s="3">
         <v>34627800</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>17118000</v>
+        <v>6993200</v>
       </c>
       <c r="E18" s="3">
-        <v>13174900</v>
+        <v>19797900</v>
       </c>
       <c r="F18" s="3">
-        <v>14508500</v>
+        <v>9835100</v>
       </c>
       <c r="G18" s="3">
-        <v>12105000</v>
+        <v>5092400</v>
       </c>
       <c r="H18" s="3">
-        <v>14352300</v>
+        <v>7654600</v>
       </c>
       <c r="I18" s="3">
-        <v>14686800</v>
+        <v>8742800</v>
       </c>
       <c r="J18" s="3">
-        <v>14440900</v>
+        <v>9578500</v>
       </c>
       <c r="K18" s="3">
         <v>13309700</v>
@@ -1186,26 +1186,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-5497000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-7080900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-6996700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-7886100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-6782900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-7113000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-6390900</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>-6904900</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12367300</v>
+        <v>7230800</v>
       </c>
       <c r="E21" s="3">
-        <v>6881400</v>
+        <v>20047000</v>
       </c>
       <c r="F21" s="3">
-        <v>8435300</v>
+        <v>10783600</v>
       </c>
       <c r="G21" s="3">
-        <v>5136900</v>
+        <v>6106400</v>
       </c>
       <c r="H21" s="3">
-        <v>8443100</v>
+        <v>8540000</v>
       </c>
       <c r="I21" s="3">
-        <v>8149600</v>
+        <v>9338200</v>
       </c>
       <c r="J21" s="3">
-        <v>8625900</v>
+        <v>10202900</v>
       </c>
       <c r="K21" s="3">
         <v>6986100</v>
@@ -1276,26 +1276,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11620900</v>
+        <v>6672900</v>
       </c>
       <c r="E23" s="3">
-        <v>6094000</v>
+        <v>18550800</v>
       </c>
       <c r="F23" s="3">
-        <v>7511700</v>
+        <v>9536000</v>
       </c>
       <c r="G23" s="3">
-        <v>4218800</v>
+        <v>4156600</v>
       </c>
       <c r="H23" s="3">
-        <v>7569300</v>
+        <v>7670300</v>
       </c>
       <c r="I23" s="3">
-        <v>7573800</v>
+        <v>7829200</v>
       </c>
       <c r="J23" s="3">
-        <v>8050000</v>
+        <v>9708200</v>
       </c>
       <c r="K23" s="3">
         <v>6404800</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3289600</v>
+        <v>1837100</v>
       </c>
       <c r="E24" s="3">
-        <v>1910600</v>
+        <v>5482500</v>
       </c>
       <c r="F24" s="3">
-        <v>2079000</v>
+        <v>2622500</v>
       </c>
       <c r="G24" s="3">
-        <v>1380100</v>
+        <v>1308900</v>
       </c>
       <c r="H24" s="3">
-        <v>2165400</v>
+        <v>2193900</v>
       </c>
       <c r="I24" s="3">
-        <v>2245100</v>
+        <v>2320800</v>
       </c>
       <c r="J24" s="3">
-        <v>2526400</v>
+        <v>3048800</v>
       </c>
       <c r="K24" s="3">
         <v>1755500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8331400</v>
+        <v>4835900</v>
       </c>
       <c r="E26" s="3">
-        <v>4183400</v>
+        <v>13068300</v>
       </c>
       <c r="F26" s="3">
-        <v>5432800</v>
+        <v>6913500</v>
       </c>
       <c r="G26" s="3">
-        <v>2838800</v>
+        <v>2847700</v>
       </c>
       <c r="H26" s="3">
-        <v>5404000</v>
+        <v>5476400</v>
       </c>
       <c r="I26" s="3">
-        <v>5328700</v>
+        <v>5508400</v>
       </c>
       <c r="J26" s="3">
-        <v>5523600</v>
+        <v>6659500</v>
       </c>
       <c r="K26" s="3">
         <v>4649200</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8071100</v>
+        <v>4576100</v>
       </c>
       <c r="E27" s="3">
-        <v>4068200</v>
+        <v>12959300</v>
       </c>
       <c r="F27" s="3">
-        <v>5289900</v>
+        <v>6767900</v>
       </c>
       <c r="G27" s="3">
-        <v>2752400</v>
+        <v>2752300</v>
       </c>
       <c r="H27" s="3">
-        <v>5295400</v>
+        <v>5365300</v>
       </c>
       <c r="I27" s="3">
-        <v>5209000</v>
+        <v>5384700</v>
       </c>
       <c r="J27" s="3">
-        <v>5432800</v>
+        <v>6561000</v>
       </c>
       <c r="K27" s="3">
         <v>4567900</v>
@@ -1591,20 +1591,20 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -1726,26 +1726,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>5497000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>7080900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>6996700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>7886100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>6782900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>7113000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>6390900</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>6904900</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8071100</v>
+        <v>4576100</v>
       </c>
       <c r="E33" s="3">
-        <v>4068200</v>
+        <v>12959300</v>
       </c>
       <c r="F33" s="3">
-        <v>5289900</v>
+        <v>6767900</v>
       </c>
       <c r="G33" s="3">
-        <v>2752400</v>
+        <v>2752300</v>
       </c>
       <c r="H33" s="3">
-        <v>5295400</v>
+        <v>5365300</v>
       </c>
       <c r="I33" s="3">
-        <v>5209000</v>
+        <v>5384700</v>
       </c>
       <c r="J33" s="3">
-        <v>5432800</v>
+        <v>6561000</v>
       </c>
       <c r="K33" s="3">
         <v>5046300</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8071100</v>
+        <v>4576100</v>
       </c>
       <c r="E35" s="3">
-        <v>4068200</v>
+        <v>12959300</v>
       </c>
       <c r="F35" s="3">
-        <v>5289900</v>
+        <v>6767900</v>
       </c>
       <c r="G35" s="3">
-        <v>2752400</v>
+        <v>2752300</v>
       </c>
       <c r="H35" s="3">
-        <v>5295400</v>
+        <v>5365300</v>
       </c>
       <c r="I35" s="3">
-        <v>5209000</v>
+        <v>5384700</v>
       </c>
       <c r="J35" s="3">
-        <v>5432800</v>
+        <v>6561000</v>
       </c>
       <c r="K35" s="3">
         <v>5046300</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>118428000</v>
+        <v>10520600</v>
       </c>
       <c r="E41" s="3">
-        <v>135923000</v>
+        <v>16703000</v>
       </c>
       <c r="F41" s="3">
-        <v>144112000</v>
+        <v>11180500</v>
       </c>
       <c r="G41" s="3">
-        <v>151133000</v>
+        <v>13598800</v>
       </c>
       <c r="H41" s="3">
-        <v>97843200</v>
+        <v>12712400</v>
       </c>
       <c r="I41" s="3">
-        <v>89061000</v>
+        <v>9429800</v>
       </c>
       <c r="J41" s="3">
-        <v>56266100</v>
+        <v>8960100</v>
       </c>
       <c r="K41" s="3">
         <v>50997200</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>137305000</v>
+        <v>130409000</v>
       </c>
       <c r="E42" s="3">
-        <v>126719000</v>
+        <v>116074600</v>
       </c>
       <c r="F42" s="3">
-        <v>113855000</v>
+        <v>108278200</v>
       </c>
       <c r="G42" s="3">
-        <v>115662000</v>
+        <v>121633000</v>
       </c>
       <c r="H42" s="3">
-        <v>106537000</v>
+        <v>106408900</v>
       </c>
       <c r="I42" s="3">
-        <v>133450000</v>
+        <v>137054000</v>
       </c>
       <c r="J42" s="3">
-        <v>136480000</v>
+        <v>146372500</v>
       </c>
       <c r="K42" s="3">
         <v>132471000</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>343800</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>373000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>624400</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>512500</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>281700</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>231300</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>1293200</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2129,26 +2129,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>4890000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>6172900</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>3723400</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>3752900</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>4171200</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>7347100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>10521100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>244610400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>231552800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>243071800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>273119300</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>181006600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>208623800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>190786500</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1671400</v>
+        <v>106633100</v>
       </c>
       <c r="E47" s="3">
-        <v>1661400</v>
+        <v>93775800</v>
       </c>
       <c r="F47" s="3">
-        <v>1757800</v>
+        <v>99350600</v>
       </c>
       <c r="G47" s="3">
-        <v>1633700</v>
+        <v>113169400</v>
       </c>
       <c r="H47" s="3">
-        <v>1982600</v>
+        <v>94166800</v>
       </c>
       <c r="I47" s="3">
-        <v>1332400</v>
+        <v>92455900</v>
       </c>
       <c r="J47" s="3">
-        <v>1205100</v>
+        <v>98347700</v>
       </c>
       <c r="K47" s="3">
         <v>1238000</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2672600</v>
+        <v>2651700</v>
       </c>
       <c r="E48" s="3">
-        <v>2729100</v>
+        <v>2614100</v>
       </c>
       <c r="F48" s="3">
-        <v>2814400</v>
+        <v>2860200</v>
       </c>
       <c r="G48" s="3">
-        <v>3168800</v>
+        <v>3475200</v>
       </c>
       <c r="H48" s="3">
-        <v>3564300</v>
+        <v>3559600</v>
       </c>
       <c r="I48" s="3">
-        <v>1897300</v>
+        <v>1899500</v>
       </c>
       <c r="J48" s="3">
-        <v>2066800</v>
+        <v>2162600</v>
       </c>
       <c r="K48" s="3">
         <v>2172200</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1326900</v>
+        <v>1324200</v>
       </c>
       <c r="E49" s="3">
-        <v>1220600</v>
+        <v>1177700</v>
       </c>
       <c r="F49" s="3">
-        <v>1280400</v>
+        <v>1314700</v>
       </c>
       <c r="G49" s="3">
-        <v>1544000</v>
+        <v>1705200</v>
       </c>
       <c r="H49" s="3">
-        <v>2122200</v>
+        <v>2150200</v>
       </c>
       <c r="I49" s="3">
-        <v>2036900</v>
+        <v>2105600</v>
       </c>
       <c r="J49" s="3">
-        <v>1627100</v>
+        <v>1763900</v>
       </c>
       <c r="K49" s="3">
         <v>1610100</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2031300</v>
+        <v>2492500</v>
       </c>
       <c r="E52" s="3">
-        <v>2672600</v>
+        <v>2894100</v>
       </c>
       <c r="F52" s="3">
-        <v>1927200</v>
+        <v>3095600</v>
       </c>
       <c r="G52" s="3">
-        <v>1659200</v>
+        <v>3456900</v>
       </c>
       <c r="H52" s="3">
-        <v>1593800</v>
+        <v>3705500</v>
       </c>
       <c r="I52" s="3">
-        <v>2913000</v>
+        <v>3753100</v>
       </c>
       <c r="J52" s="3">
-        <v>1506300</v>
+        <v>4289100</v>
       </c>
       <c r="K52" s="3">
         <v>1001500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1080560000</v>
+        <v>1083562500</v>
       </c>
       <c r="E54" s="3">
-        <v>1071950000</v>
+        <v>1043960700</v>
       </c>
       <c r="F54" s="3">
-        <v>1053650000</v>
+        <v>1079551900</v>
       </c>
       <c r="G54" s="3">
-        <v>1038130000</v>
+        <v>1146513800</v>
       </c>
       <c r="H54" s="3">
-        <v>987696000</v>
+        <v>1000722700</v>
       </c>
       <c r="I54" s="3">
-        <v>982474000</v>
+        <v>1012826900</v>
       </c>
       <c r="J54" s="3">
-        <v>937269000</v>
+        <v>1013302100</v>
       </c>
       <c r="K54" s="3">
         <v>916913000</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2419000</v>
+        <v>744482100</v>
       </c>
       <c r="E57" s="3">
-        <v>2266100</v>
+        <v>745357500</v>
       </c>
       <c r="F57" s="3">
-        <v>2254000</v>
+        <v>798921900</v>
       </c>
       <c r="G57" s="3">
-        <v>2251800</v>
+        <v>841272200</v>
       </c>
       <c r="H57" s="3">
-        <v>2348100</v>
+        <v>683715600</v>
       </c>
       <c r="I57" s="3">
-        <v>2584000</v>
+        <v>679023400</v>
       </c>
       <c r="J57" s="3">
-        <v>6872700</v>
+        <v>692422000</v>
       </c>
       <c r="K57" s="3">
         <v>4767500</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>54673400</v>
+        <v>132905900</v>
       </c>
       <c r="E58" s="3">
-        <v>41485200</v>
+        <v>122370400</v>
       </c>
       <c r="F58" s="3">
-        <v>42271600</v>
+        <v>106241300</v>
       </c>
       <c r="G58" s="3">
-        <v>30169900</v>
+        <v>117164500</v>
       </c>
       <c r="H58" s="3">
-        <v>57383600</v>
+        <v>127996900</v>
       </c>
       <c r="I58" s="3">
-        <v>61260200</v>
+        <v>146723200</v>
       </c>
       <c r="J58" s="3">
-        <v>49163000</v>
+        <v>87213000</v>
       </c>
       <c r="K58" s="3">
         <v>43927300</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1944900</v>
+        <v>16808900</v>
       </c>
       <c r="E59" s="3">
-        <v>1465400</v>
+        <v>10025600</v>
       </c>
       <c r="F59" s="3">
-        <v>1431000</v>
+        <v>10940500</v>
       </c>
       <c r="G59" s="3">
-        <v>1403300</v>
+        <v>9116800</v>
       </c>
       <c r="H59" s="3">
-        <v>1685800</v>
+        <v>8322300</v>
       </c>
       <c r="I59" s="3">
-        <v>1880700</v>
+        <v>12031100</v>
       </c>
       <c r="J59" s="3">
-        <v>1919500</v>
+        <v>58156800</v>
       </c>
       <c r="K59" s="3">
         <v>1129500</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>895700200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>878820100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>917264900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>968685000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>821121100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>838780600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>843302100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>101756000</v>
+        <v>111238000</v>
       </c>
       <c r="E61" s="3">
-        <v>83538500</v>
+        <v>87679800</v>
       </c>
       <c r="F61" s="3">
-        <v>79253200</v>
+        <v>88535200</v>
       </c>
       <c r="G61" s="3">
-        <v>79714000</v>
+        <v>96030600</v>
       </c>
       <c r="H61" s="3">
-        <v>93940000</v>
+        <v>104249800</v>
       </c>
       <c r="I61" s="3">
-        <v>86576700</v>
+        <v>99260400</v>
       </c>
       <c r="J61" s="3">
-        <v>74948000</v>
+        <v>92688500</v>
       </c>
       <c r="K61" s="3">
         <v>86768500</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1437700</v>
+        <v>13322600</v>
       </c>
       <c r="E62" s="3">
-        <v>1635900</v>
+        <v>13525700</v>
       </c>
       <c r="F62" s="3">
-        <v>2101100</v>
+        <v>13008100</v>
       </c>
       <c r="G62" s="3">
-        <v>1891800</v>
+        <v>12469700</v>
       </c>
       <c r="H62" s="3">
-        <v>2159800</v>
+        <v>12593400</v>
       </c>
       <c r="I62" s="3">
-        <v>2379100</v>
+        <v>16932700</v>
       </c>
       <c r="J62" s="3">
-        <v>3353800</v>
+        <v>17190200</v>
       </c>
       <c r="K62" s="3">
         <v>3762800</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1023800000</v>
+        <v>1022074700</v>
       </c>
       <c r="E66" s="3">
-        <v>1016670000</v>
+        <v>983039400</v>
       </c>
       <c r="F66" s="3">
-        <v>993929000</v>
+        <v>1019501900</v>
       </c>
       <c r="G66" s="3">
-        <v>977610000</v>
+        <v>1078429400</v>
       </c>
       <c r="H66" s="3">
-        <v>928141000</v>
+        <v>939380500</v>
       </c>
       <c r="I66" s="3">
-        <v>926062000</v>
+        <v>955748800</v>
       </c>
       <c r="J66" s="3">
-        <v>881439000</v>
+        <v>954291500</v>
       </c>
       <c r="K66" s="3">
         <v>862888000</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>44194300</v>
+        <v>44544000</v>
       </c>
       <c r="E72" s="3">
-        <v>42695800</v>
+        <v>44392400</v>
       </c>
       <c r="F72" s="3">
-        <v>45114800</v>
+        <v>40329800</v>
       </c>
       <c r="G72" s="3">
-        <v>42559500</v>
+        <v>43033600</v>
       </c>
       <c r="H72" s="3">
-        <v>39709700</v>
+        <v>36654700</v>
       </c>
       <c r="I72" s="3">
-        <v>36771200</v>
+        <v>32446800</v>
       </c>
       <c r="J72" s="3">
-        <v>34918200</v>
+        <v>32447200</v>
       </c>
       <c r="K72" s="3">
         <v>31619100</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>56753400</v>
+        <v>60444300</v>
       </c>
       <c r="E76" s="3">
-        <v>55279200</v>
+        <v>60382600</v>
       </c>
       <c r="F76" s="3">
-        <v>59719600</v>
+        <v>59213000</v>
       </c>
       <c r="G76" s="3">
-        <v>60515900</v>
+        <v>66834300</v>
       </c>
       <c r="H76" s="3">
-        <v>59554500</v>
+        <v>60340000</v>
       </c>
       <c r="I76" s="3">
-        <v>56412300</v>
+        <v>56158700</v>
       </c>
       <c r="J76" s="3">
-        <v>55829700</v>
+        <v>58152000</v>
       </c>
       <c r="K76" s="3">
         <v>54025400</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8071100</v>
+        <v>4576100</v>
       </c>
       <c r="E81" s="3">
-        <v>4068200</v>
+        <v>12959300</v>
       </c>
       <c r="F81" s="3">
-        <v>5289900</v>
+        <v>6767900</v>
       </c>
       <c r="G81" s="3">
-        <v>2752400</v>
+        <v>2752300</v>
       </c>
       <c r="H81" s="3">
-        <v>5295400</v>
+        <v>5365300</v>
       </c>
       <c r="I81" s="3">
-        <v>5209000</v>
+        <v>5384700</v>
       </c>
       <c r="J81" s="3">
-        <v>5432800</v>
+        <v>6561000</v>
       </c>
       <c r="K81" s="3">
         <v>5046300</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>746500</v>
+        <v>509600</v>
       </c>
       <c r="E83" s="3">
-        <v>787500</v>
+        <v>518300</v>
       </c>
       <c r="F83" s="3">
-        <v>923700</v>
+        <v>651700</v>
       </c>
       <c r="G83" s="3">
-        <v>918200</v>
+        <v>707000</v>
       </c>
       <c r="H83" s="3">
-        <v>873900</v>
+        <v>885400</v>
       </c>
       <c r="I83" s="3">
-        <v>576000</v>
+        <v>595400</v>
       </c>
       <c r="J83" s="3">
-        <v>576000</v>
+        <v>409500</v>
       </c>
       <c r="K83" s="3">
         <v>581600</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-12560200</v>
+        <v>13209900</v>
       </c>
       <c r="E89" s="3">
-        <v>-12307700</v>
+        <v>-9824700</v>
       </c>
       <c r="F89" s="3">
-        <v>-16550900</v>
+        <v>-38348700</v>
       </c>
       <c r="G89" s="3">
-        <v>112136700</v>
+        <v>22579800</v>
       </c>
       <c r="H89" s="3">
-        <v>14459700</v>
+        <v>-2705600</v>
       </c>
       <c r="I89" s="3">
-        <v>7659100</v>
+        <v>-15346900</v>
       </c>
       <c r="J89" s="3">
-        <v>-5818200</v>
+        <v>-28270900</v>
       </c>
       <c r="K89" s="3">
         <v>9280000</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-272500</v>
+        <v>-271900</v>
       </c>
       <c r="E91" s="3">
-        <v>-255900</v>
+        <v>-246900</v>
       </c>
       <c r="F91" s="3">
-        <v>-203800</v>
+        <v>-209300</v>
       </c>
       <c r="G91" s="3">
-        <v>-317900</v>
+        <v>-351100</v>
       </c>
       <c r="H91" s="3">
-        <v>-393200</v>
+        <v>-398400</v>
       </c>
       <c r="I91" s="3">
-        <v>-316800</v>
+        <v>-327500</v>
       </c>
       <c r="J91" s="3">
-        <v>-336700</v>
+        <v>-365000</v>
       </c>
       <c r="K91" s="3">
         <v>-450300</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9464400</v>
+        <v>-9445100</v>
       </c>
       <c r="E94" s="3">
-        <v>-5878000</v>
+        <v>-5671700</v>
       </c>
       <c r="F94" s="3">
-        <v>6889300</v>
+        <v>7073800</v>
       </c>
       <c r="G94" s="3">
-        <v>-9400200</v>
+        <v>-10381700</v>
       </c>
       <c r="H94" s="3">
-        <v>-2763500</v>
+        <v>-2799900</v>
       </c>
       <c r="I94" s="3">
-        <v>6037500</v>
+        <v>6241100</v>
       </c>
       <c r="J94" s="3">
-        <v>13018700</v>
+        <v>14113800</v>
       </c>
       <c r="K94" s="3">
         <v>6655400</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3282900</v>
+        <v>3279500</v>
       </c>
       <c r="E96" s="3">
-        <v>-3380400</v>
+        <v>3305500</v>
       </c>
       <c r="F96" s="3">
-        <v>-2594000</v>
+        <v>2663500</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2935100</v>
+        <v>2973900</v>
       </c>
       <c r="I96" s="3">
-        <v>-2887500</v>
+        <v>2984900</v>
       </c>
       <c r="J96" s="3">
-        <v>-2839900</v>
+        <v>3078800</v>
       </c>
       <c r="K96" s="3">
         <v>-2735300</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>20384300</v>
+        <v>-5401800</v>
       </c>
       <c r="E100" s="3">
-        <v>5149200</v>
+        <v>2917600</v>
       </c>
       <c r="F100" s="3">
-        <v>5966600</v>
+        <v>27481000</v>
       </c>
       <c r="G100" s="3">
-        <v>-38540000</v>
+        <v>58700900</v>
       </c>
       <c r="H100" s="3">
-        <v>-4601000</v>
+        <v>12694400</v>
       </c>
       <c r="I100" s="3">
-        <v>17702800</v>
+        <v>41564000</v>
       </c>
       <c r="J100" s="3">
-        <v>-4372800</v>
+        <v>17222600</v>
       </c>
       <c r="K100" s="3">
         <v>-20676800</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-994600</v>
+        <v>-992600</v>
       </c>
       <c r="E101" s="3">
-        <v>-558200</v>
+        <v>-538600</v>
       </c>
       <c r="F101" s="3">
-        <v>-625800</v>
+        <v>-642600</v>
       </c>
       <c r="G101" s="3">
-        <v>-470700</v>
+        <v>-519900</v>
       </c>
       <c r="H101" s="3">
-        <v>105200</v>
+        <v>106600</v>
       </c>
       <c r="I101" s="3">
-        <v>226000</v>
+        <v>233600</v>
       </c>
       <c r="J101" s="3">
-        <v>288000</v>
+        <v>312200</v>
       </c>
       <c r="K101" s="3">
         <v>168200</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2635000</v>
+        <v>-2629600</v>
       </c>
       <c r="E102" s="3">
-        <v>-13594700</v>
+        <v>-13117500</v>
       </c>
       <c r="F102" s="3">
-        <v>-4320700</v>
+        <v>-4436500</v>
       </c>
       <c r="G102" s="3">
-        <v>63725800</v>
+        <v>70379200</v>
       </c>
       <c r="H102" s="3">
-        <v>7200500</v>
+        <v>7295500</v>
       </c>
       <c r="I102" s="3">
-        <v>31625300</v>
+        <v>32691800</v>
       </c>
       <c r="J102" s="3">
-        <v>3115700</v>
+        <v>3377800</v>
       </c>
       <c r="K102" s="3">
         <v>-4573300</v>

--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>ING</t>
   </si>
@@ -656,119 +656,125 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20762000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19483800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31444900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22183600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>17867900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19198700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20060700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21365300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47937500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>47284500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>54387600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61505000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65900900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>79429400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,36 +817,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20762000</v>
+      </c>
+      <c r="E10" s="3">
         <v>19483800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31444900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22183600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17867900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19198700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20060700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21365300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -856,9 +865,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,36 +981,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>448300</v>
+      </c>
+      <c r="E14" s="3">
         <v>320300</v>
       </c>
-      <c r="E14" s="3">
-        <v>1247100</v>
-      </c>
       <c r="F14" s="3">
+        <v>1192600</v>
+      </c>
+      <c r="G14" s="3">
         <v>299100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>935800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>913700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-129700</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1010,54 +1029,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E15" s="3">
         <v>237600</v>
       </c>
-      <c r="E15" s="3">
-        <v>249000</v>
-      </c>
       <c r="F15" s="3">
+        <v>759900</v>
+      </c>
+      <c r="G15" s="3">
         <v>948500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1014100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>885400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>595400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>624400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-581600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-627800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-650400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-724900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-715900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1015300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12266300</v>
+      </c>
+      <c r="E17" s="3">
         <v>12490600</v>
       </c>
-      <c r="E17" s="3">
-        <v>11647000</v>
-      </c>
       <c r="F17" s="3">
+        <v>11701500</v>
+      </c>
+      <c r="G17" s="3">
         <v>12348500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12775500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11544200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11317800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11786700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34627800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35837200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42295000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>50218900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55167900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62059300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8495700</v>
+      </c>
+      <c r="E18" s="3">
         <v>6993200</v>
       </c>
-      <c r="E18" s="3">
-        <v>19797900</v>
-      </c>
       <c r="F18" s="3">
+        <v>19743400</v>
+      </c>
+      <c r="G18" s="3">
         <v>9835100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5092400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7654600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8742800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9578500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13309700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11447300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12092700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11286100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10733000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17370000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,8 +1213,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1207,72 +1240,78 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-6904900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5146900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7907100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4141200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7016200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-11411800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8719300</v>
+      </c>
+      <c r="E21" s="3">
         <v>7230800</v>
       </c>
-      <c r="E21" s="3">
-        <v>20047000</v>
-      </c>
       <c r="F21" s="3">
+        <v>20503300</v>
+      </c>
+      <c r="G21" s="3">
         <v>10783600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6106400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8540000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9338200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10202900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6986100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6935100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4968700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8056200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>7736600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1297,8 +1336,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1315,99 +1354,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8047400</v>
+      </c>
+      <c r="E23" s="3">
         <v>6672900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18550800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9536000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4156600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7670300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7829200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9708200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6404800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6300400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4185600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7144900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3716700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5958300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2258000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1837100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5482500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2622500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1308900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2193900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2320800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3048800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1755500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1671000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1096400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1791900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>939900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1232500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5789400</v>
+      </c>
+      <c r="E26" s="3">
         <v>4835900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13068300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6913500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2847700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5476400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5508400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6659500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4649200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4629300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3089200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5353000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2776800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4725800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5522300</v>
+      </c>
+      <c r="E27" s="3">
         <v>4576100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12959300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6767900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2752300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5365300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5384700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6561000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4567900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4558900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2153200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4628100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1860000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2750200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,26 +1673,29 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>478500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-465500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1587500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>592100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1405400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1753700</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,9 +1786,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1747,72 +1816,78 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>6904900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5146900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7907100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4141200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7016200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>11411800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5522300</v>
+      </c>
+      <c r="E33" s="3">
         <v>4576100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12959300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6767900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2752300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5365300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5384700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6561000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5046300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4093400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>565700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5220200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3265500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4503900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5522300</v>
+      </c>
+      <c r="E35" s="3">
         <v>4576100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12959300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6767900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2752300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5365300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5384700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6561000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5046300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4093400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>565700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5220200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3265500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4503900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,125 +2074,132 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6861000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10520600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16703000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11180500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13598800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12712400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9429800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8960100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50997200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>105032000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>111447000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>134721000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>143923000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126432000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>130409000</v>
+        <v>140094200</v>
       </c>
       <c r="E42" s="3">
+        <v>130397900</v>
+      </c>
+      <c r="F42" s="3">
         <v>116074600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>108278200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>121633000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>106408900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>137054000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>146372500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>132471000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>140919000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>162702000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>395158000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>256626000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>308386000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>502100</v>
+      </c>
+      <c r="E43" s="3">
         <v>343800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>373000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>624400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>512500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>281700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>231300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1293200</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2123,9 +2215,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2150,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2168,36 +2263,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4210600</v>
+      </c>
+      <c r="E45" s="3">
         <v>4890000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6172900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3723400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3752900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4171200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7347100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10521100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2213,36 +2311,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>244610400</v>
+        <v>223229100</v>
       </c>
       <c r="E46" s="3">
+        <v>244599300</v>
+      </c>
+      <c r="F46" s="3">
         <v>231552800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>243071800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>273119300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>181006600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>208623800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>190786500</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2258,144 +2359,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>106633100</v>
+        <v>107750300</v>
       </c>
       <c r="E47" s="3">
+        <v>106644200</v>
+      </c>
+      <c r="F47" s="3">
         <v>93775800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>99350600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>113169400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>94166800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>92455900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>98347700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1238000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>982000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1076000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2418700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7928700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9163900</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2519900</v>
+      </c>
+      <c r="E48" s="3">
         <v>2651700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2614100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2860200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3475200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3559600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1899500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2162600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2172200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4216900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4832500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7103000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11519100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10695800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1381100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1324200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1177700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1314700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1705200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2150200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2105600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1763900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1610100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2620400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5520200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2418700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8692900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8352800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2553100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2492500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2894100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3095600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3456900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3705500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3753100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4289100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1001500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3685100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>188860000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>190519000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>84463700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>91383500</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1060002100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1083562500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1043960700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1079551900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1146513800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1000722700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1012826900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1013302100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>916913000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1026140000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1330820000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1287850000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1271540000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1495710000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,170 +2786,180 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>733392700</v>
+      </c>
+      <c r="E57" s="3">
         <v>744482100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>745357500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>798921900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>841272200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>683715600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>679023400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>692422000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4767500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5263200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6483300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9421300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11604800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13731200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>124762400</v>
+      </c>
+      <c r="E58" s="3">
         <v>132905900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>122370400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>106241300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>117164500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127996900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>146723200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>87213000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>43927300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>52276200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61522400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63118700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>113681000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10289900</v>
+      </c>
+      <c r="E59" s="3">
         <v>16808900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10025600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10940500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9116800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8322300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12031100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>58156800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1129500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1179000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1167500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1522800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14712100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16799600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>870187400</v>
+      </c>
+      <c r="E60" s="3">
         <v>895700200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>878820100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>917264900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>968685000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>821121100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>838780600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>843302100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2836,99 +2975,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>121654400</v>
+      </c>
+      <c r="E61" s="3">
         <v>111238000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>87679800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>88535200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>96030600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>104249800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>99260400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>92688500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>86768500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>88288000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>163166000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>114304000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>185502000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>197673000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11118100</v>
+      </c>
+      <c r="E62" s="3">
         <v>13322600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13525700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13008100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12469700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12593400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16932700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>17190200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3762800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2148800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3208900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>624400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5090300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7349200</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1004408300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1022074700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>983039400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1019501900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1078429400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>939380500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>955748800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>954291500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>862888000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>977315000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1272850000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1235490000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1218060000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1441920000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37522500</v>
+      </c>
+      <c r="E72" s="3">
         <v>44544000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44392400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>40329800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>43033600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>36654700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32446800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32447200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31619100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27381900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27824400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24640500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43774000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>46677700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54563600</v>
+      </c>
+      <c r="E76" s="3">
         <v>60444300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>60382600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>59213000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66834300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>60340000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>56158700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58152000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>54025400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48826900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57972500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52363700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53480300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53792200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5522300</v>
+      </c>
+      <c r="E81" s="3">
         <v>4576100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12959300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6767900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2752300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5365300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5384700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6561000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5046300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4093400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>565700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5220200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3265500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4503900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>473100</v>
+      </c>
+      <c r="E83" s="3">
         <v>509600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>518300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>651700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>707000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>885400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>595400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>409500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>581600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>647200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>781300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>915100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1777100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-57786500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13209900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-9824700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-38348700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22579800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2705600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15346900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28270900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9280000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10797000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13570700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10069600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10167500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16596500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-343700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-271900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-246900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-209300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-351100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-398400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-327500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-365000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-450300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-398100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-461800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-562200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-464500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1980200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6246000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9445100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5671700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7073800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10381700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2799900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6241100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>14113800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>6655400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4283300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8376800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11087600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>7634500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,41 +4455,42 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4015900</v>
+      </c>
+      <c r="E96" s="3">
         <v>3279500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3305500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2663500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>2973900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2984900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3078800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2735300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1422000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>40010400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5401800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2917600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>27481000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>58700900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12694400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>41564000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>17222600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20676800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11397200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5265000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10410500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-8135700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-766100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-992600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-538600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-642600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-519900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>106600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>233600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>312200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>168200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-349100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1055000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-234800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24788300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2629600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13117500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4436500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>70379200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7295500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>32691800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3377800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4573300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3333900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-75600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8337500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11122700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15860500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ING_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ING_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>ING</t>
   </si>
@@ -656,125 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>28717900</v>
+      </c>
+      <c r="E8" s="3">
         <v>20762000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19483800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>31444900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22183600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17867900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19198700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20060700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21365300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>47937500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>47284500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>54387600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61505000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65900900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>79429400</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -820,39 +826,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28717900</v>
+      </c>
+      <c r="E10" s="3">
         <v>20762000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19483800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>31444900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22183600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17867900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19198700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20060700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21365300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -868,9 +877,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,39 +1000,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>448300</v>
+        <v>738300</v>
       </c>
       <c r="E14" s="3">
-        <v>320300</v>
+        <v>551800</v>
       </c>
       <c r="F14" s="3">
+        <v>29600</v>
+      </c>
+      <c r="G14" s="3">
         <v>1192600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>299100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>935800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-15700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>913700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-129700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1032,57 +1051,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>240700</v>
+      </c>
+      <c r="E15" s="3">
         <v>223600</v>
       </c>
-      <c r="E15" s="3">
-        <v>237600</v>
-      </c>
       <c r="F15" s="3">
+        <v>745000</v>
+      </c>
+      <c r="G15" s="3">
         <v>759900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>948500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1014100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>885400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>595400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>624400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-581600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-627800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-650400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-724900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-715900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1015300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12266300</v>
+        <v>14135500</v>
       </c>
       <c r="E17" s="3">
-        <v>12490600</v>
+        <v>12162700</v>
       </c>
       <c r="F17" s="3">
+        <v>12781300</v>
+      </c>
+      <c r="G17" s="3">
         <v>11701500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12348500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12775500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11544200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11317800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11786700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>34627800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35837200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42295000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>50218900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55167900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62059300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8495700</v>
+        <v>14582400</v>
       </c>
       <c r="E18" s="3">
-        <v>6993200</v>
+        <v>8599200</v>
       </c>
       <c r="F18" s="3">
+        <v>6702500</v>
+      </c>
+      <c r="G18" s="3">
         <v>19743400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9835100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5092400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7654600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8742800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9578500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13309700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11447300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12092700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11286100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10733000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17370000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,8 +1246,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1243,75 +1276,81 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-6904900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5146900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7907100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4141200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7016200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11411800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8719300</v>
+        <v>14823000</v>
       </c>
       <c r="E21" s="3">
-        <v>7230800</v>
+        <v>8822900</v>
       </c>
       <c r="F21" s="3">
+        <v>7447500</v>
+      </c>
+      <c r="G21" s="3">
         <v>20503300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10783600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6106400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8540000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9338200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10202900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6986100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6935100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4968700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8056200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>7736600</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1339,8 +1378,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1357,105 +1396,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>13844100</v>
+      </c>
+      <c r="E23" s="3">
         <v>8047400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6672900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18550800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9536000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4156600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7670300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7829200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9708200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6404800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6300400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4185600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7144900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3716700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5958300</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3747800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2258000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1837100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5482500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2622500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1308900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2193900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2320800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3048800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1755500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1671000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1096400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1791900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>939900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1232500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10096300</v>
+      </c>
+      <c r="E26" s="3">
         <v>5789400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4835900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13068300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6913500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2847700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5476400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5508400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6659500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4649200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4629300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3089200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5353000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2776800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4725800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9773400</v>
+      </c>
+      <c r="E27" s="3">
         <v>5522300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4576100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12959300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6767900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2752300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5365300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5384700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6561000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4567900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4558900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2153200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4628100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1860000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2750200</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,26 +1736,29 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>478500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-465500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1587500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>592100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1405400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1753700</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,9 +1855,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,75 +1888,81 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>6904900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5146900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7907100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4141200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7016200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11411800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9773400</v>
+      </c>
+      <c r="E33" s="3">
         <v>5522300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4576100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12959300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6767900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2752300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5365300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5384700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6561000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5046300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4093400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>565700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5220200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3265500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4503900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9773400</v>
+      </c>
+      <c r="E35" s="3">
         <v>5522300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4576100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12959300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6767900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2752300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5365300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5384700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6561000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5046300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4093400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>565700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5220200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3265500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4503900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,134 +2160,141 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11835200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6861000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10520600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16703000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11180500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13598800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12712400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9429800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8960100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50997200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>105032000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111447000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>134721000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>143923000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126432000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>156879200</v>
+      </c>
+      <c r="E42" s="3">
         <v>140094200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130397900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>116074600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>108278200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>121633000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>106408900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>137054000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>146372500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>132471000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>140919000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>162702000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>395158000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>256626000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>308386000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>537700</v>
+      </c>
+      <c r="E43" s="3">
         <v>502100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>343800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>373000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>624400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>512500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>281700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>231300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1293200</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2218,9 +2310,12 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,39 +2361,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5561800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4210600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4890000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6172900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3723400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3752900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4171200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7347100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10521100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2314,39 +2412,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>235823600</v>
+      </c>
+      <c r="E46" s="3">
         <v>223229100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>244599300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>231552800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>243071800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>273119300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>181006600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>208623800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>190786500</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2362,153 +2463,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>135664000</v>
+      </c>
+      <c r="E47" s="3">
         <v>107750300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>106644200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>93775800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>99350600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>113169400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>94166800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>92455900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>98347700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1238000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>982000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1076000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2418700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7928700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9163900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2909500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2519900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2651700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2614100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2860200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3475200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3559600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1899500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2162600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2172200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4216900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4832500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7103000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11519100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10695800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1772900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1381100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1324200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1177700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1314700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1705200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2150200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2105600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1763900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1610100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2620400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5520200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2418700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8692900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8352800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2829600</v>
+      </c>
+      <c r="E52" s="3">
         <v>2553100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2492500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2894100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3095600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3456900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3705500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3753100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4289100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1001500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3685100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>188860000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>190519000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>84463700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>91383500</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1244956000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1060002100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1083562500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1043960700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1079551900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1146513800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1000722700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1012826900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1013302100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>916913000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1026140000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1330820000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1287850000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1271540000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1495710000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,182 +2916,192 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>868721400</v>
+      </c>
+      <c r="E57" s="3">
         <v>733392700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>744482100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>745357500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>798921900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>841272200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>683715600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>679023400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>692422000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4767500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5263200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6483300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9421300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11604800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13731200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>154100000</v>
+      </c>
+      <c r="E58" s="3">
         <v>124762400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>132905900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>122370400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>106241300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>117164500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>127996900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>146723200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>87213000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>43927300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>52276200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>61522400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63118700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>113681000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4520400</v>
+      </c>
+      <c r="E59" s="3">
         <v>10289900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16808900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10025600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10940500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9116800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8322300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12031100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>58156800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1129500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1179000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1167500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1522800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14712100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16799600</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3">
         <v>870187400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>895700200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>878820100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>917264900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>968685000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>821121100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>838780600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>843302100</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2978,105 +3117,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>136436500</v>
+      </c>
+      <c r="E61" s="3">
         <v>121654400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>111238000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87679800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>88535200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>96030600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>104249800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>99260400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>92688500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>86768500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>88288000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>163166000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>114304000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>185502000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>197673000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11843400</v>
+      </c>
+      <c r="E62" s="3">
         <v>11118100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13322600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13525700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13008100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12469700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12593400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16932700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>17190200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3762800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2148800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3208900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>624400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5090300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7349200</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1179982400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1004408300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1022074700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>983039400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1019501900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1078429400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>939380500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>955748800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>954291500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>862888000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>977315000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1272850000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1235490000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1218060000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1441920000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>46983700</v>
+      </c>
+      <c r="E72" s="3">
         <v>37522500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44544000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>44392400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40329800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43033600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>36654700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32446800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32447200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31619100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27381900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27824400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24640500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43774000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46677700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63500100</v>
+      </c>
+      <c r="E76" s="3">
         <v>54563600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>60444300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>60382600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>59213000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66834300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>60340000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>56158700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58152000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54025400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48826900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>57972500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52363700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53480300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53792200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9773400</v>
+      </c>
+      <c r="E81" s="3">
         <v>5522300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4576100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12959300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6767900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2752300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5365300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5384700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6561000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5046300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4093400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>565700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5220200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3265500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4503900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>519000</v>
+      </c>
+      <c r="E83" s="3">
         <v>473100</v>
       </c>
-      <c r="E83" s="3">
-        <v>509600</v>
-      </c>
       <c r="F83" s="3">
+        <v>504000</v>
+      </c>
+      <c r="G83" s="3">
         <v>518300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>651700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>707000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>885400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>595400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>409500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>581600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>647200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>781300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>915100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>1777100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-51291500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-57786500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13209900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9824700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-38348700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22579800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2705600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15346900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-28270900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9280000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>10797000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13570700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10069600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10167500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>16596500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-412100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-343700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-271900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-246900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-209300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-351100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-398400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-327500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-365000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-450300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-398100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-461800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-562200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-464500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1980200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18430200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6246000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9445100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5671700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>7073800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10381700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2799900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>6241100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>14113800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>6655400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4283300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8376800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>11087600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>7634500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,44 +4688,45 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4560300</v>
+      </c>
+      <c r="E96" s="3">
         <v>4015900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3279500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3305500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2663500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2973900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2984900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3078800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2735300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1422000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>53481300</v>
+      </c>
+      <c r="E100" s="3">
         <v>40010400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5401800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2917600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>27481000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>58700900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12694400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>41564000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17222600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-20676800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11397200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5265000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10410500</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-8135700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1278600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-766100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-992600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-538600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-642600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-519900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>106600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>233600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>312200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>168200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-349100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1055000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-234800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17519100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24788300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2629600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13117500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4436500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>70379200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7295500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>32691800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3377800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4573300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3333900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-75600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8337500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11122700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15860500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
